--- a/data/house/house.xlsx
+++ b/data/house/house.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\conta\git-CVC\Formation\Python\Industrie\git_indus\data\house\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8002A50F-7BB2-446A-8FED-D1D1CB787C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE9D68EA-A56E-4967-8170-226BB2633C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="house" sheetId="1" r:id="rId1"/>
@@ -3970,1206 +3970,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1048576"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>26</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>29</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>31</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>33</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>34</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>35</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>36</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>37</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>38</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>39</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>41</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>42</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>43</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>44</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>45</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>46</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>47</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>48</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>49</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>50</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>51</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>52</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>53</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>54</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>55</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>56</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>57</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>58</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>60</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>61</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>62</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>63</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>65</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>66</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>67</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>68</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>69</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>70</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>71</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>72</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>73</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>74</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>75</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>76</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>77</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>78</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>79</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>80</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>81</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>82</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>83</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>84</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>85</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>86</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>87</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>88</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>89</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>90</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>91</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>92</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>93</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>94</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>95</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>96</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>97</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>98</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>101</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>102</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>104</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>105</c:v>
-                </c:pt>
-                <c:pt idx="105">
-                  <c:v>106</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>107</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>108</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>109</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>110</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>111</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>112</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>113</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>114</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>115</c:v>
-                </c:pt>
-                <c:pt idx="115">
-                  <c:v>116</c:v>
-                </c:pt>
-                <c:pt idx="116">
-                  <c:v>117</c:v>
-                </c:pt>
-                <c:pt idx="117">
-                  <c:v>118</c:v>
-                </c:pt>
-                <c:pt idx="118">
-                  <c:v>119</c:v>
-                </c:pt>
-                <c:pt idx="119">
-                  <c:v>120</c:v>
-                </c:pt>
-                <c:pt idx="120">
-                  <c:v>121</c:v>
-                </c:pt>
-                <c:pt idx="121">
-                  <c:v>122</c:v>
-                </c:pt>
-                <c:pt idx="122">
-                  <c:v>123</c:v>
-                </c:pt>
-                <c:pt idx="123">
-                  <c:v>124</c:v>
-                </c:pt>
-                <c:pt idx="124">
-                  <c:v>125</c:v>
-                </c:pt>
-                <c:pt idx="125">
-                  <c:v>126</c:v>
-                </c:pt>
-                <c:pt idx="126">
-                  <c:v>127</c:v>
-                </c:pt>
-                <c:pt idx="127">
-                  <c:v>128</c:v>
-                </c:pt>
-                <c:pt idx="128">
-                  <c:v>129</c:v>
-                </c:pt>
-                <c:pt idx="129">
-                  <c:v>130</c:v>
-                </c:pt>
-                <c:pt idx="130">
-                  <c:v>131</c:v>
-                </c:pt>
-                <c:pt idx="131">
-                  <c:v>132</c:v>
-                </c:pt>
-                <c:pt idx="132">
-                  <c:v>133</c:v>
-                </c:pt>
-                <c:pt idx="133">
-                  <c:v>134</c:v>
-                </c:pt>
-                <c:pt idx="134">
-                  <c:v>135</c:v>
-                </c:pt>
-                <c:pt idx="135">
-                  <c:v>136</c:v>
-                </c:pt>
-                <c:pt idx="136">
-                  <c:v>137</c:v>
-                </c:pt>
-                <c:pt idx="137">
-                  <c:v>138</c:v>
-                </c:pt>
-                <c:pt idx="138">
-                  <c:v>139</c:v>
-                </c:pt>
-                <c:pt idx="139">
-                  <c:v>140</c:v>
-                </c:pt>
-                <c:pt idx="140">
-                  <c:v>141</c:v>
-                </c:pt>
-                <c:pt idx="141">
-                  <c:v>142</c:v>
-                </c:pt>
-                <c:pt idx="142">
-                  <c:v>143</c:v>
-                </c:pt>
-                <c:pt idx="143">
-                  <c:v>144</c:v>
-                </c:pt>
-                <c:pt idx="144">
-                  <c:v>145</c:v>
-                </c:pt>
-                <c:pt idx="145">
-                  <c:v>146</c:v>
-                </c:pt>
-                <c:pt idx="146">
-                  <c:v>147</c:v>
-                </c:pt>
-                <c:pt idx="147">
-                  <c:v>148</c:v>
-                </c:pt>
-                <c:pt idx="148">
-                  <c:v>149</c:v>
-                </c:pt>
-                <c:pt idx="149">
-                  <c:v>150</c:v>
-                </c:pt>
-                <c:pt idx="150">
-                  <c:v>151</c:v>
-                </c:pt>
-                <c:pt idx="151">
-                  <c:v>152</c:v>
-                </c:pt>
-                <c:pt idx="152">
-                  <c:v>153</c:v>
-                </c:pt>
-                <c:pt idx="153">
-                  <c:v>154</c:v>
-                </c:pt>
-                <c:pt idx="154">
-                  <c:v>155</c:v>
-                </c:pt>
-                <c:pt idx="155">
-                  <c:v>156</c:v>
-                </c:pt>
-                <c:pt idx="156">
-                  <c:v>157</c:v>
-                </c:pt>
-                <c:pt idx="157">
-                  <c:v>158</c:v>
-                </c:pt>
-                <c:pt idx="158">
-                  <c:v>159</c:v>
-                </c:pt>
-                <c:pt idx="159">
-                  <c:v>160</c:v>
-                </c:pt>
-                <c:pt idx="160">
-                  <c:v>161</c:v>
-                </c:pt>
-                <c:pt idx="161">
-                  <c:v>162</c:v>
-                </c:pt>
-                <c:pt idx="162">
-                  <c:v>163</c:v>
-                </c:pt>
-                <c:pt idx="163">
-                  <c:v>164</c:v>
-                </c:pt>
-                <c:pt idx="164">
-                  <c:v>165</c:v>
-                </c:pt>
-                <c:pt idx="165">
-                  <c:v>166</c:v>
-                </c:pt>
-                <c:pt idx="166">
-                  <c:v>167</c:v>
-                </c:pt>
-                <c:pt idx="167">
-                  <c:v>168</c:v>
-                </c:pt>
-                <c:pt idx="168">
-                  <c:v>169</c:v>
-                </c:pt>
-                <c:pt idx="169">
-                  <c:v>170</c:v>
-                </c:pt>
-                <c:pt idx="170">
-                  <c:v>171</c:v>
-                </c:pt>
-                <c:pt idx="171">
-                  <c:v>172</c:v>
-                </c:pt>
-                <c:pt idx="172">
-                  <c:v>173</c:v>
-                </c:pt>
-                <c:pt idx="173">
-                  <c:v>174</c:v>
-                </c:pt>
-                <c:pt idx="174">
-                  <c:v>175</c:v>
-                </c:pt>
-                <c:pt idx="175">
-                  <c:v>176</c:v>
-                </c:pt>
-                <c:pt idx="176">
-                  <c:v>177</c:v>
-                </c:pt>
-                <c:pt idx="177">
-                  <c:v>178</c:v>
-                </c:pt>
-                <c:pt idx="178">
-                  <c:v>179</c:v>
-                </c:pt>
-                <c:pt idx="179">
-                  <c:v>180</c:v>
-                </c:pt>
-                <c:pt idx="180">
-                  <c:v>181</c:v>
-                </c:pt>
-                <c:pt idx="181">
-                  <c:v>182</c:v>
-                </c:pt>
-                <c:pt idx="182">
-                  <c:v>183</c:v>
-                </c:pt>
-                <c:pt idx="183">
-                  <c:v>184</c:v>
-                </c:pt>
-                <c:pt idx="184">
-                  <c:v>185</c:v>
-                </c:pt>
-                <c:pt idx="185">
-                  <c:v>186</c:v>
-                </c:pt>
-                <c:pt idx="186">
-                  <c:v>187</c:v>
-                </c:pt>
-                <c:pt idx="187">
-                  <c:v>188</c:v>
-                </c:pt>
-                <c:pt idx="188">
-                  <c:v>189</c:v>
-                </c:pt>
-                <c:pt idx="189">
-                  <c:v>190</c:v>
-                </c:pt>
-                <c:pt idx="190">
-                  <c:v>191</c:v>
-                </c:pt>
-                <c:pt idx="191">
-                  <c:v>192</c:v>
-                </c:pt>
-                <c:pt idx="192">
-                  <c:v>193</c:v>
-                </c:pt>
-                <c:pt idx="193">
-                  <c:v>194</c:v>
-                </c:pt>
-                <c:pt idx="194">
-                  <c:v>195</c:v>
-                </c:pt>
-                <c:pt idx="195">
-                  <c:v>196</c:v>
-                </c:pt>
-                <c:pt idx="196">
-                  <c:v>197</c:v>
-                </c:pt>
-                <c:pt idx="197">
-                  <c:v>198</c:v>
-                </c:pt>
-                <c:pt idx="198">
-                  <c:v>199</c:v>
-                </c:pt>
-                <c:pt idx="199">
-                  <c:v>200</c:v>
-                </c:pt>
-                <c:pt idx="200">
-                  <c:v>201</c:v>
-                </c:pt>
-                <c:pt idx="201">
-                  <c:v>202</c:v>
-                </c:pt>
-                <c:pt idx="202">
-                  <c:v>203</c:v>
-                </c:pt>
-                <c:pt idx="203">
-                  <c:v>204</c:v>
-                </c:pt>
-                <c:pt idx="204">
-                  <c:v>205</c:v>
-                </c:pt>
-                <c:pt idx="205">
-                  <c:v>206</c:v>
-                </c:pt>
-                <c:pt idx="206">
-                  <c:v>207</c:v>
-                </c:pt>
-                <c:pt idx="207">
-                  <c:v>208</c:v>
-                </c:pt>
-                <c:pt idx="208">
-                  <c:v>209</c:v>
-                </c:pt>
-                <c:pt idx="209">
-                  <c:v>210</c:v>
-                </c:pt>
-                <c:pt idx="210">
-                  <c:v>211</c:v>
-                </c:pt>
-                <c:pt idx="211">
-                  <c:v>212</c:v>
-                </c:pt>
-                <c:pt idx="212">
-                  <c:v>213</c:v>
-                </c:pt>
-                <c:pt idx="213">
-                  <c:v>214</c:v>
-                </c:pt>
-                <c:pt idx="214">
-                  <c:v>215</c:v>
-                </c:pt>
-                <c:pt idx="215">
-                  <c:v>216</c:v>
-                </c:pt>
-                <c:pt idx="216">
-                  <c:v>217</c:v>
-                </c:pt>
-                <c:pt idx="217">
-                  <c:v>218</c:v>
-                </c:pt>
-                <c:pt idx="218">
-                  <c:v>219</c:v>
-                </c:pt>
-                <c:pt idx="219">
-                  <c:v>220</c:v>
-                </c:pt>
-                <c:pt idx="220">
-                  <c:v>221</c:v>
-                </c:pt>
-                <c:pt idx="221">
-                  <c:v>222</c:v>
-                </c:pt>
-                <c:pt idx="222">
-                  <c:v>223</c:v>
-                </c:pt>
-                <c:pt idx="223">
-                  <c:v>224</c:v>
-                </c:pt>
-                <c:pt idx="224">
-                  <c:v>225</c:v>
-                </c:pt>
-                <c:pt idx="225">
-                  <c:v>226</c:v>
-                </c:pt>
-                <c:pt idx="226">
-                  <c:v>227</c:v>
-                </c:pt>
-                <c:pt idx="227">
-                  <c:v>228</c:v>
-                </c:pt>
-                <c:pt idx="228">
-                  <c:v>229</c:v>
-                </c:pt>
-                <c:pt idx="229">
-                  <c:v>230</c:v>
-                </c:pt>
-                <c:pt idx="230">
-                  <c:v>231</c:v>
-                </c:pt>
-                <c:pt idx="231">
-                  <c:v>232</c:v>
-                </c:pt>
-                <c:pt idx="232">
-                  <c:v>233</c:v>
-                </c:pt>
-                <c:pt idx="233">
-                  <c:v>234</c:v>
-                </c:pt>
-                <c:pt idx="234">
-                  <c:v>235</c:v>
-                </c:pt>
-                <c:pt idx="235">
-                  <c:v>236</c:v>
-                </c:pt>
-                <c:pt idx="236">
-                  <c:v>237</c:v>
-                </c:pt>
-                <c:pt idx="237">
-                  <c:v>238</c:v>
-                </c:pt>
-                <c:pt idx="238">
-                  <c:v>239</c:v>
-                </c:pt>
-                <c:pt idx="239">
-                  <c:v>240</c:v>
-                </c:pt>
-                <c:pt idx="240">
-                  <c:v>241</c:v>
-                </c:pt>
-                <c:pt idx="241">
-                  <c:v>242</c:v>
-                </c:pt>
-                <c:pt idx="242">
-                  <c:v>243</c:v>
-                </c:pt>
-                <c:pt idx="243">
-                  <c:v>244</c:v>
-                </c:pt>
-                <c:pt idx="244">
-                  <c:v>245</c:v>
-                </c:pt>
-                <c:pt idx="245">
-                  <c:v>246</c:v>
-                </c:pt>
-                <c:pt idx="246">
-                  <c:v>247</c:v>
-                </c:pt>
-                <c:pt idx="247">
-                  <c:v>248</c:v>
-                </c:pt>
-                <c:pt idx="248">
-                  <c:v>249</c:v>
-                </c:pt>
-                <c:pt idx="249">
-                  <c:v>250</c:v>
-                </c:pt>
-                <c:pt idx="250">
-                  <c:v>251</c:v>
-                </c:pt>
-                <c:pt idx="251">
-                  <c:v>252</c:v>
-                </c:pt>
-                <c:pt idx="252">
-                  <c:v>253</c:v>
-                </c:pt>
-                <c:pt idx="253">
-                  <c:v>254</c:v>
-                </c:pt>
-                <c:pt idx="254">
-                  <c:v>255</c:v>
-                </c:pt>
-                <c:pt idx="255">
-                  <c:v>256</c:v>
-                </c:pt>
-                <c:pt idx="256">
-                  <c:v>257</c:v>
-                </c:pt>
-                <c:pt idx="257">
-                  <c:v>258</c:v>
-                </c:pt>
-                <c:pt idx="258">
-                  <c:v>259</c:v>
-                </c:pt>
-                <c:pt idx="259">
-                  <c:v>260</c:v>
-                </c:pt>
-                <c:pt idx="260">
-                  <c:v>261</c:v>
-                </c:pt>
-                <c:pt idx="261">
-                  <c:v>262</c:v>
-                </c:pt>
-                <c:pt idx="262">
-                  <c:v>263</c:v>
-                </c:pt>
-                <c:pt idx="263">
-                  <c:v>264</c:v>
-                </c:pt>
-                <c:pt idx="264">
-                  <c:v>265</c:v>
-                </c:pt>
-                <c:pt idx="265">
-                  <c:v>266</c:v>
-                </c:pt>
-                <c:pt idx="266">
-                  <c:v>267</c:v>
-                </c:pt>
-                <c:pt idx="267">
-                  <c:v>268</c:v>
-                </c:pt>
-                <c:pt idx="268">
-                  <c:v>269</c:v>
-                </c:pt>
-                <c:pt idx="269">
-                  <c:v>270</c:v>
-                </c:pt>
-                <c:pt idx="270">
-                  <c:v>271</c:v>
-                </c:pt>
-                <c:pt idx="271">
-                  <c:v>272</c:v>
-                </c:pt>
-                <c:pt idx="272">
-                  <c:v>273</c:v>
-                </c:pt>
-                <c:pt idx="273">
-                  <c:v>274</c:v>
-                </c:pt>
-                <c:pt idx="274">
-                  <c:v>275</c:v>
-                </c:pt>
-                <c:pt idx="275">
-                  <c:v>276</c:v>
-                </c:pt>
-                <c:pt idx="276">
-                  <c:v>277</c:v>
-                </c:pt>
-                <c:pt idx="277">
-                  <c:v>278</c:v>
-                </c:pt>
-                <c:pt idx="278">
-                  <c:v>279</c:v>
-                </c:pt>
-                <c:pt idx="279">
-                  <c:v>280</c:v>
-                </c:pt>
-                <c:pt idx="280">
-                  <c:v>281</c:v>
-                </c:pt>
-                <c:pt idx="281">
-                  <c:v>282</c:v>
-                </c:pt>
-                <c:pt idx="282">
-                  <c:v>283</c:v>
-                </c:pt>
-                <c:pt idx="283">
-                  <c:v>284</c:v>
-                </c:pt>
-                <c:pt idx="284">
-                  <c:v>285</c:v>
-                </c:pt>
-                <c:pt idx="285">
-                  <c:v>286</c:v>
-                </c:pt>
-                <c:pt idx="286">
-                  <c:v>287</c:v>
-                </c:pt>
-                <c:pt idx="287">
-                  <c:v>288</c:v>
-                </c:pt>
-                <c:pt idx="288">
-                  <c:v>289</c:v>
-                </c:pt>
-                <c:pt idx="289">
-                  <c:v>290</c:v>
-                </c:pt>
-                <c:pt idx="290">
-                  <c:v>291</c:v>
-                </c:pt>
-                <c:pt idx="291">
-                  <c:v>292</c:v>
-                </c:pt>
-                <c:pt idx="292">
-                  <c:v>293</c:v>
-                </c:pt>
-                <c:pt idx="293">
-                  <c:v>294</c:v>
-                </c:pt>
-                <c:pt idx="294">
-                  <c:v>295</c:v>
-                </c:pt>
-                <c:pt idx="295">
-                  <c:v>296</c:v>
-                </c:pt>
-                <c:pt idx="296">
-                  <c:v>297</c:v>
-                </c:pt>
-                <c:pt idx="297">
-                  <c:v>298</c:v>
-                </c:pt>
-                <c:pt idx="298">
-                  <c:v>299</c:v>
-                </c:pt>
-                <c:pt idx="299">
-                  <c:v>300</c:v>
-                </c:pt>
-                <c:pt idx="300">
-                  <c:v>301</c:v>
-                </c:pt>
-                <c:pt idx="301">
-                  <c:v>302</c:v>
-                </c:pt>
-                <c:pt idx="302">
-                  <c:v>303</c:v>
-                </c:pt>
-                <c:pt idx="303">
-                  <c:v>304</c:v>
-                </c:pt>
-                <c:pt idx="304">
-                  <c:v>305</c:v>
-                </c:pt>
-                <c:pt idx="305">
-                  <c:v>306</c:v>
-                </c:pt>
-                <c:pt idx="306">
-                  <c:v>307</c:v>
-                </c:pt>
-                <c:pt idx="307">
-                  <c:v>308</c:v>
-                </c:pt>
-                <c:pt idx="308">
-                  <c:v>309</c:v>
-                </c:pt>
-                <c:pt idx="309">
-                  <c:v>310</c:v>
-                </c:pt>
-                <c:pt idx="310">
-                  <c:v>311</c:v>
-                </c:pt>
-                <c:pt idx="311">
-                  <c:v>312</c:v>
-                </c:pt>
-                <c:pt idx="312">
-                  <c:v>313</c:v>
-                </c:pt>
-                <c:pt idx="313">
-                  <c:v>314</c:v>
-                </c:pt>
-                <c:pt idx="314">
-                  <c:v>315</c:v>
-                </c:pt>
-                <c:pt idx="315">
-                  <c:v>316</c:v>
-                </c:pt>
-                <c:pt idx="316">
-                  <c:v>317</c:v>
-                </c:pt>
-                <c:pt idx="317">
-                  <c:v>318</c:v>
-                </c:pt>
-                <c:pt idx="318">
-                  <c:v>319</c:v>
-                </c:pt>
-                <c:pt idx="319">
-                  <c:v>320</c:v>
-                </c:pt>
-                <c:pt idx="320">
-                  <c:v>321</c:v>
-                </c:pt>
-                <c:pt idx="321">
-                  <c:v>322</c:v>
-                </c:pt>
-                <c:pt idx="322">
-                  <c:v>323</c:v>
-                </c:pt>
-                <c:pt idx="323">
-                  <c:v>324</c:v>
-                </c:pt>
-                <c:pt idx="324">
-                  <c:v>325</c:v>
-                </c:pt>
-                <c:pt idx="325">
-                  <c:v>326</c:v>
-                </c:pt>
-                <c:pt idx="326">
-                  <c:v>327</c:v>
-                </c:pt>
-                <c:pt idx="327">
-                  <c:v>328</c:v>
-                </c:pt>
-                <c:pt idx="328">
-                  <c:v>329</c:v>
-                </c:pt>
-                <c:pt idx="329">
-                  <c:v>330</c:v>
-                </c:pt>
-                <c:pt idx="330">
-                  <c:v>331</c:v>
-                </c:pt>
-                <c:pt idx="331">
-                  <c:v>332</c:v>
-                </c:pt>
-                <c:pt idx="332">
-                  <c:v>333</c:v>
-                </c:pt>
-                <c:pt idx="333">
-                  <c:v>334</c:v>
-                </c:pt>
-                <c:pt idx="334">
-                  <c:v>335</c:v>
-                </c:pt>
-                <c:pt idx="335">
-                  <c:v>336</c:v>
-                </c:pt>
-                <c:pt idx="336">
-                  <c:v>337</c:v>
-                </c:pt>
-                <c:pt idx="337">
-                  <c:v>338</c:v>
-                </c:pt>
-                <c:pt idx="338">
-                  <c:v>339</c:v>
-                </c:pt>
-                <c:pt idx="339">
-                  <c:v>340</c:v>
-                </c:pt>
-                <c:pt idx="340">
-                  <c:v>341</c:v>
-                </c:pt>
-                <c:pt idx="341">
-                  <c:v>342</c:v>
-                </c:pt>
-                <c:pt idx="342">
-                  <c:v>343</c:v>
-                </c:pt>
-                <c:pt idx="343">
-                  <c:v>344</c:v>
-                </c:pt>
-                <c:pt idx="344">
-                  <c:v>345</c:v>
-                </c:pt>
-                <c:pt idx="345">
-                  <c:v>346</c:v>
-                </c:pt>
-                <c:pt idx="346">
-                  <c:v>347</c:v>
-                </c:pt>
-                <c:pt idx="347">
-                  <c:v>348</c:v>
-                </c:pt>
-                <c:pt idx="348">
-                  <c:v>349</c:v>
-                </c:pt>
-                <c:pt idx="349">
-                  <c:v>350</c:v>
-                </c:pt>
-                <c:pt idx="350">
-                  <c:v>351</c:v>
-                </c:pt>
-                <c:pt idx="351">
-                  <c:v>352</c:v>
-                </c:pt>
-                <c:pt idx="352">
-                  <c:v>353</c:v>
-                </c:pt>
-                <c:pt idx="353">
-                  <c:v>354</c:v>
-                </c:pt>
-                <c:pt idx="354">
-                  <c:v>355</c:v>
-                </c:pt>
-                <c:pt idx="355">
-                  <c:v>356</c:v>
-                </c:pt>
-                <c:pt idx="356">
-                  <c:v>357</c:v>
-                </c:pt>
-                <c:pt idx="357">
-                  <c:v>358</c:v>
-                </c:pt>
-                <c:pt idx="358">
-                  <c:v>359</c:v>
-                </c:pt>
-                <c:pt idx="359">
-                  <c:v>360</c:v>
-                </c:pt>
-                <c:pt idx="360">
-                  <c:v>361</c:v>
-                </c:pt>
-                <c:pt idx="361">
-                  <c:v>362</c:v>
-                </c:pt>
-                <c:pt idx="362">
-                  <c:v>363</c:v>
-                </c:pt>
-                <c:pt idx="363">
-                  <c:v>364</c:v>
-                </c:pt>
-                <c:pt idx="364">
-                  <c:v>365</c:v>
-                </c:pt>
-                <c:pt idx="365">
-                  <c:v>366</c:v>
-                </c:pt>
-                <c:pt idx="366">
-                  <c:v>367</c:v>
-                </c:pt>
-                <c:pt idx="367">
-                  <c:v>368</c:v>
-                </c:pt>
-                <c:pt idx="368">
-                  <c:v>369</c:v>
-                </c:pt>
-                <c:pt idx="369">
-                  <c:v>370</c:v>
-                </c:pt>
-                <c:pt idx="370">
-                  <c:v>371</c:v>
-                </c:pt>
-                <c:pt idx="371">
-                  <c:v>372</c:v>
-                </c:pt>
-                <c:pt idx="372">
-                  <c:v>373</c:v>
-                </c:pt>
-                <c:pt idx="373">
-                  <c:v>374</c:v>
-                </c:pt>
-                <c:pt idx="374">
-                  <c:v>375</c:v>
-                </c:pt>
-                <c:pt idx="375">
-                  <c:v>376</c:v>
-                </c:pt>
-                <c:pt idx="376">
-                  <c:v>377</c:v>
-                </c:pt>
-                <c:pt idx="377">
-                  <c:v>378</c:v>
-                </c:pt>
-                <c:pt idx="378">
-                  <c:v>379</c:v>
-                </c:pt>
-                <c:pt idx="379">
-                  <c:v>380</c:v>
-                </c:pt>
-                <c:pt idx="380">
-                  <c:v>381</c:v>
-                </c:pt>
-                <c:pt idx="381">
-                  <c:v>382</c:v>
-                </c:pt>
-                <c:pt idx="382">
-                  <c:v>383</c:v>
-                </c:pt>
-                <c:pt idx="383">
-                  <c:v>384</c:v>
-                </c:pt>
-                <c:pt idx="384">
-                  <c:v>385</c:v>
-                </c:pt>
-                <c:pt idx="385">
-                  <c:v>386</c:v>
-                </c:pt>
-                <c:pt idx="386">
-                  <c:v>387</c:v>
-                </c:pt>
-                <c:pt idx="387">
-                  <c:v>388</c:v>
-                </c:pt>
-                <c:pt idx="388">
-                  <c:v>389</c:v>
-                </c:pt>
-                <c:pt idx="389">
-                  <c:v>390</c:v>
-                </c:pt>
-                <c:pt idx="390">
-                  <c:v>391</c:v>
-                </c:pt>
-                <c:pt idx="391">
-                  <c:v>392</c:v>
-                </c:pt>
-                <c:pt idx="392">
-                  <c:v>393</c:v>
-                </c:pt>
-                <c:pt idx="393">
-                  <c:v>394</c:v>
-                </c:pt>
-                <c:pt idx="394">
-                  <c:v>395</c:v>
-                </c:pt>
-                <c:pt idx="395">
-                  <c:v>396</c:v>
-                </c:pt>
-                <c:pt idx="396">
-                  <c:v>397</c:v>
-                </c:pt>
-                <c:pt idx="397">
-                  <c:v>398</c:v>
-                </c:pt>
-                <c:pt idx="398">
-                  <c:v>399</c:v>
-                </c:pt>
-                <c:pt idx="399">
-                  <c:v>400</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -5179,1206 +3979,6 @@
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="1048576"/>
-                <c:pt idx="0">
-                  <c:v>-242.78456156167363</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-201.81095782217972</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-160.83735408268583</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-119.86375034319192</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-78.890146603698014</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-37.916542864204132</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>3.0570608752897783</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>44.030664614783689</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>85.004268354277599</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>125.97787209377151</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>166.95147583326542</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>207.92507957275927</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>248.89868331225318</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>289.87228705174709</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>330.845890791241</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>371.81949453073491</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>412.79309827022882</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>453.76670200972274</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>494.74030574921665</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>535.71390948871056</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>576.68751322820447</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>617.66111696769838</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>658.63472070719229</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>699.60832444668608</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>740.58192818617999</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>781.5555319256739</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>822.52913566516781</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>863.50273940466172</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>904.47634314415563</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>945.44994688364955</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>986.42355062314346</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>1027.3971543626374</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>1068.3707581021313</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>1109.3443618416252</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>1150.3179655811191</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>1191.291569320613</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>1232.2651730601069</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>1273.2387767996008</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>1314.2123805390947</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>1355.1859842785886</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>1396.1595880180826</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>1437.1331917575765</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>1478.1067954970704</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>1519.0803992365643</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>1560.0540029760582</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>1601.0276067155521</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>1642.001210455046</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>1682.9748141945397</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>1723.9484179340336</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>1764.9220216735275</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>1805.8956254130217</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>1846.8692291525153</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>1887.8428328920095</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>1928.8164366315032</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>1969.7900403709973</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>2010.763644110491</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>2051.7372478499851</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>2092.7108515894788</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>2133.6844553289729</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>2174.6580590684666</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>2215.6316628079608</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>2256.6052665474544</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>2297.5788702869486</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>2338.5524740264423</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>2379.526077765936</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>2420.4996815054301</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>2461.4732852449238</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>2502.4468889844179</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>2543.4204927239116</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>2584.3940964634057</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>2625.3677002028994</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>2666.3413039423936</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>2707.3149076818872</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>2748.2885114213814</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>2789.2621151608751</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>2830.2357189003692</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>2871.2093226398629</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>2912.182926379357</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>2953.1565301188507</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>2994.1301338583448</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>3035.1037375978385</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>3076.0773413373327</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>3117.0509450768263</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>3158.0245488163205</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>3198.9981525558142</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>3239.9717562953083</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>3280.945360034802</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>3321.9189637742961</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>3362.8925675137898</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>3403.8661712532839</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>3444.8397749927776</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>3485.8133787322718</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>3526.7869824717654</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>3567.7605862112596</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>3608.7341899507533</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>3649.7077936902469</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>3690.6813974297411</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>3731.6550011692348</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>3772.6286049087289</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>3813.6022086482226</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>3854.5758123877167</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>3895.5494161272109</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>3936.5230198667041</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>3977.4966236061982</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>4018.4702273456924</c:v>
-                </c:pt>
-                <c:pt idx="105">
-                  <c:v>4059.4438310851865</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>4100.4174348246797</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>4141.3910385641739</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>4182.364642303668</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>4223.3382460431621</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>4264.3118497826554</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>4305.2854535221495</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>4346.2590572616436</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>4387.2326610011378</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>4428.206264740631</c:v>
-                </c:pt>
-                <c:pt idx="115">
-                  <c:v>4469.1798684801252</c:v>
-                </c:pt>
-                <c:pt idx="116">
-                  <c:v>4510.1534722196193</c:v>
-                </c:pt>
-                <c:pt idx="117">
-                  <c:v>4551.1270759591134</c:v>
-                </c:pt>
-                <c:pt idx="118">
-                  <c:v>4592.1006796986067</c:v>
-                </c:pt>
-                <c:pt idx="119">
-                  <c:v>4633.0742834381008</c:v>
-                </c:pt>
-                <c:pt idx="120">
-                  <c:v>4674.0478871775949</c:v>
-                </c:pt>
-                <c:pt idx="121">
-                  <c:v>4715.0214909170891</c:v>
-                </c:pt>
-                <c:pt idx="122">
-                  <c:v>4755.9950946565823</c:v>
-                </c:pt>
-                <c:pt idx="123">
-                  <c:v>4796.9686983960764</c:v>
-                </c:pt>
-                <c:pt idx="124">
-                  <c:v>4837.9423021355706</c:v>
-                </c:pt>
-                <c:pt idx="125">
-                  <c:v>4878.9159058750647</c:v>
-                </c:pt>
-                <c:pt idx="126">
-                  <c:v>4919.8895096145579</c:v>
-                </c:pt>
-                <c:pt idx="127">
-                  <c:v>4960.8631133540521</c:v>
-                </c:pt>
-                <c:pt idx="128">
-                  <c:v>5001.8367170935462</c:v>
-                </c:pt>
-                <c:pt idx="129">
-                  <c:v>5042.8103208330394</c:v>
-                </c:pt>
-                <c:pt idx="130">
-                  <c:v>5083.7839245725336</c:v>
-                </c:pt>
-                <c:pt idx="131">
-                  <c:v>5124.7575283120277</c:v>
-                </c:pt>
-                <c:pt idx="132">
-                  <c:v>5165.7311320515219</c:v>
-                </c:pt>
-                <c:pt idx="133">
-                  <c:v>5206.7047357910151</c:v>
-                </c:pt>
-                <c:pt idx="134">
-                  <c:v>5247.6783395305092</c:v>
-                </c:pt>
-                <c:pt idx="135">
-                  <c:v>5288.6519432700034</c:v>
-                </c:pt>
-                <c:pt idx="136">
-                  <c:v>5329.6255470094975</c:v>
-                </c:pt>
-                <c:pt idx="137">
-                  <c:v>5370.5991507489907</c:v>
-                </c:pt>
-                <c:pt idx="138">
-                  <c:v>5411.5727544884849</c:v>
-                </c:pt>
-                <c:pt idx="139">
-                  <c:v>5452.546358227979</c:v>
-                </c:pt>
-                <c:pt idx="140">
-                  <c:v>5493.5199619674731</c:v>
-                </c:pt>
-                <c:pt idx="141">
-                  <c:v>5534.4935657069664</c:v>
-                </c:pt>
-                <c:pt idx="142">
-                  <c:v>5575.4671694464605</c:v>
-                </c:pt>
-                <c:pt idx="143">
-                  <c:v>5616.4407731859546</c:v>
-                </c:pt>
-                <c:pt idx="144">
-                  <c:v>5657.4143769254488</c:v>
-                </c:pt>
-                <c:pt idx="145">
-                  <c:v>5698.387980664942</c:v>
-                </c:pt>
-                <c:pt idx="146">
-                  <c:v>5739.3615844044361</c:v>
-                </c:pt>
-                <c:pt idx="147">
-                  <c:v>5780.3351881439303</c:v>
-                </c:pt>
-                <c:pt idx="148">
-                  <c:v>5821.3087918834244</c:v>
-                </c:pt>
-                <c:pt idx="149">
-                  <c:v>5862.2823956229176</c:v>
-                </c:pt>
-                <c:pt idx="150">
-                  <c:v>5903.2559993624118</c:v>
-                </c:pt>
-                <c:pt idx="151">
-                  <c:v>5944.2296031019059</c:v>
-                </c:pt>
-                <c:pt idx="152">
-                  <c:v>5985.2032068414001</c:v>
-                </c:pt>
-                <c:pt idx="153">
-                  <c:v>6026.1768105808933</c:v>
-                </c:pt>
-                <c:pt idx="154">
-                  <c:v>6067.1504143203874</c:v>
-                </c:pt>
-                <c:pt idx="155">
-                  <c:v>6108.1240180598816</c:v>
-                </c:pt>
-                <c:pt idx="156">
-                  <c:v>6149.0976217993757</c:v>
-                </c:pt>
-                <c:pt idx="157">
-                  <c:v>6190.0712255388689</c:v>
-                </c:pt>
-                <c:pt idx="158">
-                  <c:v>6231.0448292783631</c:v>
-                </c:pt>
-                <c:pt idx="159">
-                  <c:v>6272.0184330178572</c:v>
-                </c:pt>
-                <c:pt idx="160">
-                  <c:v>6312.9920367573504</c:v>
-                </c:pt>
-                <c:pt idx="161">
-                  <c:v>6353.9656404968446</c:v>
-                </c:pt>
-                <c:pt idx="162">
-                  <c:v>6394.9392442363387</c:v>
-                </c:pt>
-                <c:pt idx="163">
-                  <c:v>6435.9128479758328</c:v>
-                </c:pt>
-                <c:pt idx="164">
-                  <c:v>6476.8864517153261</c:v>
-                </c:pt>
-                <c:pt idx="165">
-                  <c:v>6517.8600554548202</c:v>
-                </c:pt>
-                <c:pt idx="166">
-                  <c:v>6558.8336591943144</c:v>
-                </c:pt>
-                <c:pt idx="167">
-                  <c:v>6599.8072629338085</c:v>
-                </c:pt>
-                <c:pt idx="168">
-                  <c:v>6640.7808666733017</c:v>
-                </c:pt>
-                <c:pt idx="169">
-                  <c:v>6681.7544704127959</c:v>
-                </c:pt>
-                <c:pt idx="170">
-                  <c:v>6722.72807415229</c:v>
-                </c:pt>
-                <c:pt idx="171">
-                  <c:v>6763.7016778917841</c:v>
-                </c:pt>
-                <c:pt idx="172">
-                  <c:v>6804.6752816312774</c:v>
-                </c:pt>
-                <c:pt idx="173">
-                  <c:v>6845.6488853707715</c:v>
-                </c:pt>
-                <c:pt idx="174">
-                  <c:v>6886.6224891102656</c:v>
-                </c:pt>
-                <c:pt idx="175">
-                  <c:v>6927.5960928497598</c:v>
-                </c:pt>
-                <c:pt idx="176">
-                  <c:v>6968.569696589253</c:v>
-                </c:pt>
-                <c:pt idx="177">
-                  <c:v>7009.5433003287471</c:v>
-                </c:pt>
-                <c:pt idx="178">
-                  <c:v>7050.5169040682413</c:v>
-                </c:pt>
-                <c:pt idx="179">
-                  <c:v>7091.4905078077354</c:v>
-                </c:pt>
-                <c:pt idx="180">
-                  <c:v>7132.4641115472286</c:v>
-                </c:pt>
-                <c:pt idx="181">
-                  <c:v>7173.4377152867228</c:v>
-                </c:pt>
-                <c:pt idx="182">
-                  <c:v>7214.4113190262169</c:v>
-                </c:pt>
-                <c:pt idx="183">
-                  <c:v>7255.3849227657111</c:v>
-                </c:pt>
-                <c:pt idx="184">
-                  <c:v>7296.3585265052043</c:v>
-                </c:pt>
-                <c:pt idx="185">
-                  <c:v>7337.3321302446984</c:v>
-                </c:pt>
-                <c:pt idx="186">
-                  <c:v>7378.3057339841926</c:v>
-                </c:pt>
-                <c:pt idx="187">
-                  <c:v>7419.2793377236867</c:v>
-                </c:pt>
-                <c:pt idx="188">
-                  <c:v>7460.2529414631799</c:v>
-                </c:pt>
-                <c:pt idx="189">
-                  <c:v>7501.2265452026741</c:v>
-                </c:pt>
-                <c:pt idx="190">
-                  <c:v>7542.2001489421682</c:v>
-                </c:pt>
-                <c:pt idx="191">
-                  <c:v>7583.1737526816614</c:v>
-                </c:pt>
-                <c:pt idx="192">
-                  <c:v>7624.1473564211556</c:v>
-                </c:pt>
-                <c:pt idx="193">
-                  <c:v>7665.1209601606497</c:v>
-                </c:pt>
-                <c:pt idx="194">
-                  <c:v>7706.0945639001438</c:v>
-                </c:pt>
-                <c:pt idx="195">
-                  <c:v>7747.0681676396371</c:v>
-                </c:pt>
-                <c:pt idx="196">
-                  <c:v>7788.0417713791312</c:v>
-                </c:pt>
-                <c:pt idx="197">
-                  <c:v>7829.0153751186253</c:v>
-                </c:pt>
-                <c:pt idx="198">
-                  <c:v>7869.9889788581195</c:v>
-                </c:pt>
-                <c:pt idx="199">
-                  <c:v>7910.9625825976127</c:v>
-                </c:pt>
-                <c:pt idx="200">
-                  <c:v>7951.9361863371068</c:v>
-                </c:pt>
-                <c:pt idx="201">
-                  <c:v>7992.909790076601</c:v>
-                </c:pt>
-                <c:pt idx="202">
-                  <c:v>8033.8833938160951</c:v>
-                </c:pt>
-                <c:pt idx="203">
-                  <c:v>8074.8569975555893</c:v>
-                </c:pt>
-                <c:pt idx="204">
-                  <c:v>8115.8306012950834</c:v>
-                </c:pt>
-                <c:pt idx="205">
-                  <c:v>8156.8042050345757</c:v>
-                </c:pt>
-                <c:pt idx="206">
-                  <c:v>8197.7778087740699</c:v>
-                </c:pt>
-                <c:pt idx="207">
-                  <c:v>8238.751412513564</c:v>
-                </c:pt>
-                <c:pt idx="208">
-                  <c:v>8279.7250162530581</c:v>
-                </c:pt>
-                <c:pt idx="209">
-                  <c:v>8320.6986199925523</c:v>
-                </c:pt>
-                <c:pt idx="210">
-                  <c:v>8361.6722237320464</c:v>
-                </c:pt>
-                <c:pt idx="211">
-                  <c:v>8402.6458274715405</c:v>
-                </c:pt>
-                <c:pt idx="212">
-                  <c:v>8443.6194312110347</c:v>
-                </c:pt>
-                <c:pt idx="213">
-                  <c:v>8484.593034950527</c:v>
-                </c:pt>
-                <c:pt idx="214">
-                  <c:v>8525.5666386900211</c:v>
-                </c:pt>
-                <c:pt idx="215">
-                  <c:v>8566.5402424295153</c:v>
-                </c:pt>
-                <c:pt idx="216">
-                  <c:v>8607.5138461690094</c:v>
-                </c:pt>
-                <c:pt idx="217">
-                  <c:v>8648.4874499085035</c:v>
-                </c:pt>
-                <c:pt idx="218">
-                  <c:v>8689.4610536479977</c:v>
-                </c:pt>
-                <c:pt idx="219">
-                  <c:v>8730.4346573874918</c:v>
-                </c:pt>
-                <c:pt idx="220">
-                  <c:v>8771.408261126986</c:v>
-                </c:pt>
-                <c:pt idx="221">
-                  <c:v>8812.3818648664783</c:v>
-                </c:pt>
-                <c:pt idx="222">
-                  <c:v>8853.3554686059724</c:v>
-                </c:pt>
-                <c:pt idx="223">
-                  <c:v>8894.3290723454666</c:v>
-                </c:pt>
-                <c:pt idx="224">
-                  <c:v>8935.3026760849607</c:v>
-                </c:pt>
-                <c:pt idx="225">
-                  <c:v>8976.2762798244548</c:v>
-                </c:pt>
-                <c:pt idx="226">
-                  <c:v>9017.249883563949</c:v>
-                </c:pt>
-                <c:pt idx="227">
-                  <c:v>9058.2234873034431</c:v>
-                </c:pt>
-                <c:pt idx="228">
-                  <c:v>9099.1970910429354</c:v>
-                </c:pt>
-                <c:pt idx="229">
-                  <c:v>9140.1706947824296</c:v>
-                </c:pt>
-                <c:pt idx="230">
-                  <c:v>9181.1442985219237</c:v>
-                </c:pt>
-                <c:pt idx="231">
-                  <c:v>9222.1179022614178</c:v>
-                </c:pt>
-                <c:pt idx="232">
-                  <c:v>9263.091506000912</c:v>
-                </c:pt>
-                <c:pt idx="233">
-                  <c:v>9304.0651097404061</c:v>
-                </c:pt>
-                <c:pt idx="234">
-                  <c:v>9345.0387134799003</c:v>
-                </c:pt>
-                <c:pt idx="235">
-                  <c:v>9386.0123172193944</c:v>
-                </c:pt>
-                <c:pt idx="236">
-                  <c:v>9426.9859209588867</c:v>
-                </c:pt>
-                <c:pt idx="237">
-                  <c:v>9467.9595246983808</c:v>
-                </c:pt>
-                <c:pt idx="238">
-                  <c:v>9508.933128437875</c:v>
-                </c:pt>
-                <c:pt idx="239">
-                  <c:v>9549.9067321773691</c:v>
-                </c:pt>
-                <c:pt idx="240">
-                  <c:v>9590.8803359168633</c:v>
-                </c:pt>
-                <c:pt idx="241">
-                  <c:v>9631.8539396563574</c:v>
-                </c:pt>
-                <c:pt idx="242">
-                  <c:v>9672.8275433958515</c:v>
-                </c:pt>
-                <c:pt idx="243">
-                  <c:v>9713.8011471353457</c:v>
-                </c:pt>
-                <c:pt idx="244">
-                  <c:v>9754.774750874838</c:v>
-                </c:pt>
-                <c:pt idx="245">
-                  <c:v>9795.7483546143321</c:v>
-                </c:pt>
-                <c:pt idx="246">
-                  <c:v>9836.7219583538263</c:v>
-                </c:pt>
-                <c:pt idx="247">
-                  <c:v>9877.6955620933204</c:v>
-                </c:pt>
-                <c:pt idx="248">
-                  <c:v>9918.6691658328145</c:v>
-                </c:pt>
-                <c:pt idx="249">
-                  <c:v>9959.6427695723087</c:v>
-                </c:pt>
-                <c:pt idx="250">
-                  <c:v>10000.616373311803</c:v>
-                </c:pt>
-                <c:pt idx="251">
-                  <c:v>10041.589977051297</c:v>
-                </c:pt>
-                <c:pt idx="252">
-                  <c:v>10082.563580790789</c:v>
-                </c:pt>
-                <c:pt idx="253">
-                  <c:v>10123.537184530283</c:v>
-                </c:pt>
-                <c:pt idx="254">
-                  <c:v>10164.510788269778</c:v>
-                </c:pt>
-                <c:pt idx="255">
-                  <c:v>10205.484392009272</c:v>
-                </c:pt>
-                <c:pt idx="256">
-                  <c:v>10246.457995748766</c:v>
-                </c:pt>
-                <c:pt idx="257">
-                  <c:v>10287.43159948826</c:v>
-                </c:pt>
-                <c:pt idx="258">
-                  <c:v>10328.405203227754</c:v>
-                </c:pt>
-                <c:pt idx="259">
-                  <c:v>10369.378806967246</c:v>
-                </c:pt>
-                <c:pt idx="260">
-                  <c:v>10410.352410706741</c:v>
-                </c:pt>
-                <c:pt idx="261">
-                  <c:v>10451.326014446235</c:v>
-                </c:pt>
-                <c:pt idx="262">
-                  <c:v>10492.299618185729</c:v>
-                </c:pt>
-                <c:pt idx="263">
-                  <c:v>10533.273221925223</c:v>
-                </c:pt>
-                <c:pt idx="264">
-                  <c:v>10574.246825664717</c:v>
-                </c:pt>
-                <c:pt idx="265">
-                  <c:v>10615.220429404211</c:v>
-                </c:pt>
-                <c:pt idx="266">
-                  <c:v>10656.194033143705</c:v>
-                </c:pt>
-                <c:pt idx="267">
-                  <c:v>10697.167636883198</c:v>
-                </c:pt>
-                <c:pt idx="268">
-                  <c:v>10738.141240622692</c:v>
-                </c:pt>
-                <c:pt idx="269">
-                  <c:v>10779.114844362186</c:v>
-                </c:pt>
-                <c:pt idx="270">
-                  <c:v>10820.08844810168</c:v>
-                </c:pt>
-                <c:pt idx="271">
-                  <c:v>10861.062051841174</c:v>
-                </c:pt>
-                <c:pt idx="272">
-                  <c:v>10902.035655580668</c:v>
-                </c:pt>
-                <c:pt idx="273">
-                  <c:v>10943.009259320163</c:v>
-                </c:pt>
-                <c:pt idx="274">
-                  <c:v>10983.982863059657</c:v>
-                </c:pt>
-                <c:pt idx="275">
-                  <c:v>11024.956466799149</c:v>
-                </c:pt>
-                <c:pt idx="276">
-                  <c:v>11065.930070538643</c:v>
-                </c:pt>
-                <c:pt idx="277">
-                  <c:v>11106.903674278137</c:v>
-                </c:pt>
-                <c:pt idx="278">
-                  <c:v>11147.877278017631</c:v>
-                </c:pt>
-                <c:pt idx="279">
-                  <c:v>11188.850881757126</c:v>
-                </c:pt>
-                <c:pt idx="280">
-                  <c:v>11229.82448549662</c:v>
-                </c:pt>
-                <c:pt idx="281">
-                  <c:v>11270.798089236114</c:v>
-                </c:pt>
-                <c:pt idx="282">
-                  <c:v>11311.771692975608</c:v>
-                </c:pt>
-                <c:pt idx="283">
-                  <c:v>11352.7452967151</c:v>
-                </c:pt>
-                <c:pt idx="284">
-                  <c:v>11393.718900454594</c:v>
-                </c:pt>
-                <c:pt idx="285">
-                  <c:v>11434.692504194089</c:v>
-                </c:pt>
-                <c:pt idx="286">
-                  <c:v>11475.666107933583</c:v>
-                </c:pt>
-                <c:pt idx="287">
-                  <c:v>11516.639711673077</c:v>
-                </c:pt>
-                <c:pt idx="288">
-                  <c:v>11557.613315412571</c:v>
-                </c:pt>
-                <c:pt idx="289">
-                  <c:v>11598.586919152065</c:v>
-                </c:pt>
-                <c:pt idx="290">
-                  <c:v>11639.560522891557</c:v>
-                </c:pt>
-                <c:pt idx="291">
-                  <c:v>11680.534126631052</c:v>
-                </c:pt>
-                <c:pt idx="292">
-                  <c:v>11721.507730370546</c:v>
-                </c:pt>
-                <c:pt idx="293">
-                  <c:v>11762.48133411004</c:v>
-                </c:pt>
-                <c:pt idx="294">
-                  <c:v>11803.454937849534</c:v>
-                </c:pt>
-                <c:pt idx="295">
-                  <c:v>11844.428541589028</c:v>
-                </c:pt>
-                <c:pt idx="296">
-                  <c:v>11885.402145328522</c:v>
-                </c:pt>
-                <c:pt idx="297">
-                  <c:v>11926.375749068016</c:v>
-                </c:pt>
-                <c:pt idx="298">
-                  <c:v>11967.349352807509</c:v>
-                </c:pt>
-                <c:pt idx="299">
-                  <c:v>12008.322956547003</c:v>
-                </c:pt>
-                <c:pt idx="300">
-                  <c:v>12049.296560286497</c:v>
-                </c:pt>
-                <c:pt idx="301">
-                  <c:v>12090.270164025991</c:v>
-                </c:pt>
-                <c:pt idx="302">
-                  <c:v>12131.243767765485</c:v>
-                </c:pt>
-                <c:pt idx="303">
-                  <c:v>12172.217371504979</c:v>
-                </c:pt>
-                <c:pt idx="304">
-                  <c:v>12213.190975244474</c:v>
-                </c:pt>
-                <c:pt idx="305">
-                  <c:v>12254.164578983968</c:v>
-                </c:pt>
-                <c:pt idx="306">
-                  <c:v>12295.13818272346</c:v>
-                </c:pt>
-                <c:pt idx="307">
-                  <c:v>12336.111786462954</c:v>
-                </c:pt>
-                <c:pt idx="308">
-                  <c:v>12377.085390202448</c:v>
-                </c:pt>
-                <c:pt idx="309">
-                  <c:v>12418.058993941942</c:v>
-                </c:pt>
-                <c:pt idx="310">
-                  <c:v>12459.032597681437</c:v>
-                </c:pt>
-                <c:pt idx="311">
-                  <c:v>12500.006201420931</c:v>
-                </c:pt>
-                <c:pt idx="312">
-                  <c:v>12540.979805160425</c:v>
-                </c:pt>
-                <c:pt idx="313">
-                  <c:v>12581.953408899919</c:v>
-                </c:pt>
-                <c:pt idx="314">
-                  <c:v>12622.927012639411</c:v>
-                </c:pt>
-                <c:pt idx="315">
-                  <c:v>12663.900616378905</c:v>
-                </c:pt>
-                <c:pt idx="316">
-                  <c:v>12704.8742201184</c:v>
-                </c:pt>
-                <c:pt idx="317">
-                  <c:v>12745.847823857894</c:v>
-                </c:pt>
-                <c:pt idx="318">
-                  <c:v>12786.821427597388</c:v>
-                </c:pt>
-                <c:pt idx="319">
-                  <c:v>12827.795031336882</c:v>
-                </c:pt>
-                <c:pt idx="320">
-                  <c:v>12868.768635076376</c:v>
-                </c:pt>
-                <c:pt idx="321">
-                  <c:v>12909.742238815868</c:v>
-                </c:pt>
-                <c:pt idx="322">
-                  <c:v>12950.715842555363</c:v>
-                </c:pt>
-                <c:pt idx="323">
-                  <c:v>12991.689446294857</c:v>
-                </c:pt>
-                <c:pt idx="324">
-                  <c:v>13032.663050034351</c:v>
-                </c:pt>
-                <c:pt idx="325">
-                  <c:v>13073.636653773845</c:v>
-                </c:pt>
-                <c:pt idx="326">
-                  <c:v>13114.610257513339</c:v>
-                </c:pt>
-                <c:pt idx="327">
-                  <c:v>13155.583861252833</c:v>
-                </c:pt>
-                <c:pt idx="328">
-                  <c:v>13196.557464992327</c:v>
-                </c:pt>
-                <c:pt idx="329">
-                  <c:v>13237.53106873182</c:v>
-                </c:pt>
-                <c:pt idx="330">
-                  <c:v>13278.504672471314</c:v>
-                </c:pt>
-                <c:pt idx="331">
-                  <c:v>13319.478276210808</c:v>
-                </c:pt>
-                <c:pt idx="332">
-                  <c:v>13360.451879950302</c:v>
-                </c:pt>
-                <c:pt idx="333">
-                  <c:v>13401.425483689796</c:v>
-                </c:pt>
-                <c:pt idx="334">
-                  <c:v>13442.39908742929</c:v>
-                </c:pt>
-                <c:pt idx="335">
-                  <c:v>13483.372691168785</c:v>
-                </c:pt>
-                <c:pt idx="336">
-                  <c:v>13524.346294908279</c:v>
-                </c:pt>
-                <c:pt idx="337">
-                  <c:v>13565.319898647771</c:v>
-                </c:pt>
-                <c:pt idx="338">
-                  <c:v>13606.293502387265</c:v>
-                </c:pt>
-                <c:pt idx="339">
-                  <c:v>13647.267106126759</c:v>
-                </c:pt>
-                <c:pt idx="340">
-                  <c:v>13688.240709866253</c:v>
-                </c:pt>
-                <c:pt idx="341">
-                  <c:v>13729.214313605748</c:v>
-                </c:pt>
-                <c:pt idx="342">
-                  <c:v>13770.187917345242</c:v>
-                </c:pt>
-                <c:pt idx="343">
-                  <c:v>13811.161521084736</c:v>
-                </c:pt>
-                <c:pt idx="344">
-                  <c:v>13852.13512482423</c:v>
-                </c:pt>
-                <c:pt idx="345">
-                  <c:v>13893.108728563722</c:v>
-                </c:pt>
-                <c:pt idx="346">
-                  <c:v>13934.082332303216</c:v>
-                </c:pt>
-                <c:pt idx="347">
-                  <c:v>13975.055936042711</c:v>
-                </c:pt>
-                <c:pt idx="348">
-                  <c:v>14016.029539782205</c:v>
-                </c:pt>
-                <c:pt idx="349">
-                  <c:v>14057.003143521699</c:v>
-                </c:pt>
-                <c:pt idx="350">
-                  <c:v>14097.976747261193</c:v>
-                </c:pt>
-                <c:pt idx="351">
-                  <c:v>14138.950351000687</c:v>
-                </c:pt>
-                <c:pt idx="352">
-                  <c:v>14179.923954740179</c:v>
-                </c:pt>
-                <c:pt idx="353">
-                  <c:v>14220.897558479674</c:v>
-                </c:pt>
-                <c:pt idx="354">
-                  <c:v>14261.871162219168</c:v>
-                </c:pt>
-                <c:pt idx="355">
-                  <c:v>14302.844765958662</c:v>
-                </c:pt>
-                <c:pt idx="356">
-                  <c:v>14343.818369698156</c:v>
-                </c:pt>
-                <c:pt idx="357">
-                  <c:v>14384.79197343765</c:v>
-                </c:pt>
-                <c:pt idx="358">
-                  <c:v>14425.765577177144</c:v>
-                </c:pt>
-                <c:pt idx="359">
-                  <c:v>14466.739180916638</c:v>
-                </c:pt>
-                <c:pt idx="360">
-                  <c:v>14507.712784656131</c:v>
-                </c:pt>
-                <c:pt idx="361">
-                  <c:v>14548.686388395625</c:v>
-                </c:pt>
-                <c:pt idx="362">
-                  <c:v>14589.659992135119</c:v>
-                </c:pt>
-                <c:pt idx="363">
-                  <c:v>14630.633595874613</c:v>
-                </c:pt>
-                <c:pt idx="364">
-                  <c:v>14671.607199614107</c:v>
-                </c:pt>
-                <c:pt idx="365">
-                  <c:v>14712.580803353601</c:v>
-                </c:pt>
-                <c:pt idx="366">
-                  <c:v>14753.554407093096</c:v>
-                </c:pt>
-                <c:pt idx="367">
-                  <c:v>14794.52801083259</c:v>
-                </c:pt>
-                <c:pt idx="368">
-                  <c:v>14835.501614572082</c:v>
-                </c:pt>
-                <c:pt idx="369">
-                  <c:v>14876.475218311576</c:v>
-                </c:pt>
-                <c:pt idx="370">
-                  <c:v>14917.44882205107</c:v>
-                </c:pt>
-                <c:pt idx="371">
-                  <c:v>14958.422425790564</c:v>
-                </c:pt>
-                <c:pt idx="372">
-                  <c:v>14999.396029530059</c:v>
-                </c:pt>
-                <c:pt idx="373">
-                  <c:v>15040.369633269553</c:v>
-                </c:pt>
-                <c:pt idx="374">
-                  <c:v>15081.343237009047</c:v>
-                </c:pt>
-                <c:pt idx="375">
-                  <c:v>15122.316840748541</c:v>
-                </c:pt>
-                <c:pt idx="376">
-                  <c:v>15163.290444488033</c:v>
-                </c:pt>
-                <c:pt idx="377">
-                  <c:v>15204.264048227527</c:v>
-                </c:pt>
-                <c:pt idx="378">
-                  <c:v>15245.237651967022</c:v>
-                </c:pt>
-                <c:pt idx="379">
-                  <c:v>15286.211255706516</c:v>
-                </c:pt>
-                <c:pt idx="380">
-                  <c:v>15327.18485944601</c:v>
-                </c:pt>
-                <c:pt idx="381">
-                  <c:v>15368.158463185504</c:v>
-                </c:pt>
-                <c:pt idx="382">
-                  <c:v>15409.132066924998</c:v>
-                </c:pt>
-                <c:pt idx="383">
-                  <c:v>15450.10567066449</c:v>
-                </c:pt>
-                <c:pt idx="384">
-                  <c:v>15491.079274403985</c:v>
-                </c:pt>
-                <c:pt idx="385">
-                  <c:v>15532.052878143479</c:v>
-                </c:pt>
-                <c:pt idx="386">
-                  <c:v>15573.026481882973</c:v>
-                </c:pt>
-                <c:pt idx="387">
-                  <c:v>15614.000085622467</c:v>
-                </c:pt>
-                <c:pt idx="388">
-                  <c:v>15654.973689361961</c:v>
-                </c:pt>
-                <c:pt idx="389">
-                  <c:v>15695.947293101455</c:v>
-                </c:pt>
-                <c:pt idx="390">
-                  <c:v>15736.920896840949</c:v>
-                </c:pt>
-                <c:pt idx="391">
-                  <c:v>15777.894500580442</c:v>
-                </c:pt>
-                <c:pt idx="392">
-                  <c:v>15818.868104319936</c:v>
-                </c:pt>
-                <c:pt idx="393">
-                  <c:v>15859.84170805943</c:v>
-                </c:pt>
-                <c:pt idx="394">
-                  <c:v>15900.815311798924</c:v>
-                </c:pt>
-                <c:pt idx="395">
-                  <c:v>15941.788915538418</c:v>
-                </c:pt>
-                <c:pt idx="396">
-                  <c:v>15982.762519277912</c:v>
-                </c:pt>
-                <c:pt idx="397">
-                  <c:v>16023.736123017406</c:v>
-                </c:pt>
-                <c:pt idx="398">
-                  <c:v>16064.709726756901</c:v>
-                </c:pt>
-                <c:pt idx="399">
-                  <c:v>16105.683330496393</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -11814,4013 +9414,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BFFF5B0-594D-4D72-8DA1-9DC10F207B07}">
-  <dimension ref="A1:B400"/>
+  <dimension ref="B1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.5546875" style="1"/>
   </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1">
-        <f>1</f>
-        <v>1</v>
-      </c>
-      <c r="B1" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A1,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>-242.78456156167363</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <f>A1+1</f>
-        <v>2</v>
-      </c>
-      <c r="B2" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A2,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>-201.81095782217972</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <f t="shared" ref="A3:A66" si="0">A2+1</f>
-        <v>3</v>
-      </c>
-      <c r="B3" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A3,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>-160.83735408268583</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="B4" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A4,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>-119.86375034319192</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="B5" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A5,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>-78.890146603698014</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="B6" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A6,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>-37.916542864204132</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="B7" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A7,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>3.0570608752897783</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="B8" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A8,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>44.030664614783689</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="B9" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A9,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>85.004268354277599</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="B10" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A10,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>125.97787209377151</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <f>A10+1</f>
-        <v>11</v>
-      </c>
-      <c r="B11" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A11,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>166.95147583326542</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="B12" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A12,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>207.92507957275927</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="B13" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A13,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>248.89868331225318</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="B14" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A14,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>289.87228705174709</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="B15" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A15,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>330.845890791241</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="B16" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A16,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>371.81949453073491</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="B17" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A17,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>412.79309827022882</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="B18" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A18,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>453.76670200972274</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="B19" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A19,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>494.74030574921665</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="B20" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A20,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>535.71390948871056</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="B21" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A21,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>576.68751322820447</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="B22" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A22,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>617.66111696769838</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="B23" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A23,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>658.63472070719229</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="B24" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A24,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>699.60832444668608</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="B25" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A25,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>740.58192818617999</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="B26" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A26,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>781.5555319256739</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="B27" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A27,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>822.52913566516781</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="B28" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A28,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>863.50273940466172</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="B29" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A29,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>904.47634314415563</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="B30" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A30,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>945.44994688364955</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="B31" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A31,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>986.42355062314346</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="B32" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A32,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>1027.3971543626374</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33">
-        <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-      <c r="B33" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A33,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>1068.3707581021313</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34">
-        <f t="shared" si="0"/>
-        <v>34</v>
-      </c>
-      <c r="B34" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A34,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>1109.3443618416252</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-      <c r="B35" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A35,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>1150.3179655811191</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36">
-        <f t="shared" si="0"/>
-        <v>36</v>
-      </c>
-      <c r="B36" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A36,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>1191.291569320613</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37">
-        <f t="shared" si="0"/>
-        <v>37</v>
-      </c>
-      <c r="B37" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A37,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>1232.2651730601069</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38">
-        <f t="shared" si="0"/>
-        <v>38</v>
-      </c>
-      <c r="B38" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A38,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>1273.2387767996008</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39">
-        <f t="shared" si="0"/>
-        <v>39</v>
-      </c>
-      <c r="B39" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A39,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>1314.2123805390947</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="B40" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A40,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>1355.1859842785886</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41">
-        <f t="shared" si="0"/>
-        <v>41</v>
-      </c>
-      <c r="B41" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A41,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>1396.1595880180826</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42">
-        <f t="shared" si="0"/>
-        <v>42</v>
-      </c>
-      <c r="B42" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A42,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>1437.1331917575765</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43">
-        <f t="shared" si="0"/>
-        <v>43</v>
-      </c>
-      <c r="B43" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A43,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>1478.1067954970704</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44">
-        <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-      <c r="B44" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A44,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>1519.0803992365643</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45">
-        <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
-      <c r="B45" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A45,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>1560.0540029760582</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46">
-        <f t="shared" si="0"/>
-        <v>46</v>
-      </c>
-      <c r="B46" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A46,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>1601.0276067155521</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47">
-        <f t="shared" si="0"/>
-        <v>47</v>
-      </c>
-      <c r="B47" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A47,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>1642.001210455046</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48">
-        <f t="shared" si="0"/>
-        <v>48</v>
-      </c>
-      <c r="B48" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A48,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>1682.9748141945397</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49">
-        <f t="shared" si="0"/>
-        <v>49</v>
-      </c>
-      <c r="B49" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A49,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>1723.9484179340336</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="B50" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A50,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>1764.9220216735275</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51">
-        <f t="shared" si="0"/>
-        <v>51</v>
-      </c>
-      <c r="B51" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A51,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>1805.8956254130217</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52">
-        <f t="shared" si="0"/>
-        <v>52</v>
-      </c>
-      <c r="B52" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A52,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>1846.8692291525153</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53">
-        <f t="shared" si="0"/>
-        <v>53</v>
-      </c>
-      <c r="B53" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A53,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>1887.8428328920095</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54">
-        <f t="shared" si="0"/>
-        <v>54</v>
-      </c>
-      <c r="B54" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A54,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>1928.8164366315032</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55">
-        <f t="shared" si="0"/>
-        <v>55</v>
-      </c>
-      <c r="B55" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A55,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>1969.7900403709973</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56">
-        <f t="shared" si="0"/>
-        <v>56</v>
-      </c>
-      <c r="B56" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A56,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>2010.763644110491</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57">
-        <f t="shared" si="0"/>
-        <v>57</v>
-      </c>
-      <c r="B57" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A57,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>2051.7372478499851</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58">
-        <f t="shared" si="0"/>
-        <v>58</v>
-      </c>
-      <c r="B58" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A58,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>2092.7108515894788</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59">
-        <f t="shared" si="0"/>
-        <v>59</v>
-      </c>
-      <c r="B59" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A59,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>2133.6844553289729</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-      <c r="B60" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A60,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>2174.6580590684666</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61">
-        <f t="shared" si="0"/>
-        <v>61</v>
-      </c>
-      <c r="B61" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A61,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>2215.6316628079608</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62">
-        <f t="shared" si="0"/>
-        <v>62</v>
-      </c>
-      <c r="B62" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A62,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>2256.6052665474544</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63">
-        <f t="shared" si="0"/>
-        <v>63</v>
-      </c>
-      <c r="B63" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A63,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>2297.5788702869486</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64">
-        <f t="shared" si="0"/>
-        <v>64</v>
-      </c>
-      <c r="B64" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A64,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>2338.5524740264423</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65">
-        <f t="shared" si="0"/>
-        <v>65</v>
-      </c>
-      <c r="B65" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A65,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>2379.526077765936</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66">
-        <f t="shared" si="0"/>
-        <v>66</v>
-      </c>
-      <c r="B66" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A66,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>2420.4996815054301</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67">
-        <f t="shared" ref="A67:A130" si="1">A66+1</f>
-        <v>67</v>
-      </c>
-      <c r="B67" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A67,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>2461.4732852449238</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68">
-        <f t="shared" si="1"/>
-        <v>68</v>
-      </c>
-      <c r="B68" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A68,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>2502.4468889844179</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69">
-        <f t="shared" si="1"/>
-        <v>69</v>
-      </c>
-      <c r="B69" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A69,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>2543.4204927239116</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70">
-        <f t="shared" si="1"/>
-        <v>70</v>
-      </c>
-      <c r="B70" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A70,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>2584.3940964634057</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71">
-        <f t="shared" si="1"/>
-        <v>71</v>
-      </c>
-      <c r="B71" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A71,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>2625.3677002028994</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72">
-        <f t="shared" si="1"/>
-        <v>72</v>
-      </c>
-      <c r="B72" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A72,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>2666.3413039423936</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73">
-        <f t="shared" si="1"/>
-        <v>73</v>
-      </c>
-      <c r="B73" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A73,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>2707.3149076818872</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74">
-        <f t="shared" si="1"/>
-        <v>74</v>
-      </c>
-      <c r="B74" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A74,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>2748.2885114213814</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75">
-        <f t="shared" si="1"/>
-        <v>75</v>
-      </c>
-      <c r="B75" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A75,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>2789.2621151608751</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76">
-        <f t="shared" si="1"/>
-        <v>76</v>
-      </c>
-      <c r="B76" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A76,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>2830.2357189003692</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77">
-        <f t="shared" si="1"/>
-        <v>77</v>
-      </c>
-      <c r="B77" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A77,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>2871.2093226398629</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78">
-        <f t="shared" si="1"/>
-        <v>78</v>
-      </c>
-      <c r="B78" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A78,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>2912.182926379357</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79">
-        <f t="shared" si="1"/>
-        <v>79</v>
-      </c>
-      <c r="B79" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A79,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>2953.1565301188507</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80">
-        <f t="shared" si="1"/>
-        <v>80</v>
-      </c>
-      <c r="B80" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A80,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>2994.1301338583448</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A81">
-        <f t="shared" si="1"/>
-        <v>81</v>
-      </c>
-      <c r="B81" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A81,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>3035.1037375978385</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A82">
-        <f t="shared" si="1"/>
-        <v>82</v>
-      </c>
-      <c r="B82" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A82,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>3076.0773413373327</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A83">
-        <f t="shared" si="1"/>
-        <v>83</v>
-      </c>
-      <c r="B83" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A83,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>3117.0509450768263</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A84">
-        <f t="shared" si="1"/>
-        <v>84</v>
-      </c>
-      <c r="B84" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A84,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>3158.0245488163205</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A85">
-        <f t="shared" si="1"/>
-        <v>85</v>
-      </c>
-      <c r="B85" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A85,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>3198.9981525558142</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A86">
-        <f t="shared" si="1"/>
-        <v>86</v>
-      </c>
-      <c r="B86" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A86,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>3239.9717562953083</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A87">
-        <f t="shared" si="1"/>
-        <v>87</v>
-      </c>
-      <c r="B87" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A87,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>3280.945360034802</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A88">
-        <f t="shared" si="1"/>
-        <v>88</v>
-      </c>
-      <c r="B88" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A88,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>3321.9189637742961</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A89">
-        <f t="shared" si="1"/>
-        <v>89</v>
-      </c>
-      <c r="B89" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A89,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>3362.8925675137898</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A90">
-        <f t="shared" si="1"/>
-        <v>90</v>
-      </c>
-      <c r="B90" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A90,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>3403.8661712532839</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A91">
-        <f t="shared" si="1"/>
-        <v>91</v>
-      </c>
-      <c r="B91" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A91,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>3444.8397749927776</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A92">
-        <f t="shared" si="1"/>
-        <v>92</v>
-      </c>
-      <c r="B92" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A92,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>3485.8133787322718</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A93">
-        <f t="shared" si="1"/>
-        <v>93</v>
-      </c>
-      <c r="B93" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A93,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>3526.7869824717654</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A94">
-        <f t="shared" si="1"/>
-        <v>94</v>
-      </c>
-      <c r="B94" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A94,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>3567.7605862112596</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A95">
-        <f t="shared" si="1"/>
-        <v>95</v>
-      </c>
-      <c r="B95" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A95,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>3608.7341899507533</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A96">
-        <f t="shared" si="1"/>
-        <v>96</v>
-      </c>
-      <c r="B96" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A96,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>3649.7077936902469</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A97">
-        <f t="shared" si="1"/>
-        <v>97</v>
-      </c>
-      <c r="B97" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A97,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>3690.6813974297411</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A98">
-        <f t="shared" si="1"/>
-        <v>98</v>
-      </c>
-      <c r="B98" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A98,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>3731.6550011692348</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A99">
-        <f t="shared" si="1"/>
-        <v>99</v>
-      </c>
-      <c r="B99" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A99,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>3772.6286049087289</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A100">
-        <f t="shared" si="1"/>
-        <v>100</v>
-      </c>
-      <c r="B100" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A100,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>3813.6022086482226</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A101">
-        <f t="shared" si="1"/>
-        <v>101</v>
-      </c>
-      <c r="B101" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A101,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>3854.5758123877167</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A102">
-        <f t="shared" si="1"/>
-        <v>102</v>
-      </c>
-      <c r="B102" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A102,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>3895.5494161272109</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A103">
-        <f t="shared" si="1"/>
-        <v>103</v>
-      </c>
-      <c r="B103" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A103,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>3936.5230198667041</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A104">
-        <f t="shared" si="1"/>
-        <v>104</v>
-      </c>
-      <c r="B104" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A104,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>3977.4966236061982</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A105">
-        <f t="shared" si="1"/>
-        <v>105</v>
-      </c>
-      <c r="B105" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A105,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>4018.4702273456924</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A106">
-        <f t="shared" si="1"/>
-        <v>106</v>
-      </c>
-      <c r="B106" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A106,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>4059.4438310851865</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A107">
-        <f t="shared" si="1"/>
-        <v>107</v>
-      </c>
-      <c r="B107" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A107,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>4100.4174348246797</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A108">
-        <f t="shared" si="1"/>
-        <v>108</v>
-      </c>
-      <c r="B108" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A108,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>4141.3910385641739</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A109">
-        <f t="shared" si="1"/>
-        <v>109</v>
-      </c>
-      <c r="B109" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A109,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>4182.364642303668</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A110">
-        <f t="shared" si="1"/>
-        <v>110</v>
-      </c>
-      <c r="B110" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A110,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>4223.3382460431621</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A111">
-        <f t="shared" si="1"/>
-        <v>111</v>
-      </c>
-      <c r="B111" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A111,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>4264.3118497826554</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A112">
-        <f t="shared" si="1"/>
-        <v>112</v>
-      </c>
-      <c r="B112" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A112,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>4305.2854535221495</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A113">
-        <f t="shared" si="1"/>
-        <v>113</v>
-      </c>
-      <c r="B113" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A113,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>4346.2590572616436</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A114">
-        <f t="shared" si="1"/>
-        <v>114</v>
-      </c>
-      <c r="B114" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A114,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>4387.2326610011378</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A115">
-        <f t="shared" si="1"/>
-        <v>115</v>
-      </c>
-      <c r="B115" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A115,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>4428.206264740631</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A116">
-        <f t="shared" si="1"/>
-        <v>116</v>
-      </c>
-      <c r="B116" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A116,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>4469.1798684801252</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A117">
-        <f t="shared" si="1"/>
-        <v>117</v>
-      </c>
-      <c r="B117" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A117,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>4510.1534722196193</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A118">
-        <f t="shared" si="1"/>
-        <v>118</v>
-      </c>
-      <c r="B118" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A118,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>4551.1270759591134</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A119">
-        <f t="shared" si="1"/>
-        <v>119</v>
-      </c>
-      <c r="B119" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A119,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>4592.1006796986067</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A120">
-        <f t="shared" si="1"/>
-        <v>120</v>
-      </c>
-      <c r="B120" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A120,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>4633.0742834381008</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A121">
-        <f t="shared" si="1"/>
-        <v>121</v>
-      </c>
-      <c r="B121" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A121,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>4674.0478871775949</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A122">
-        <f t="shared" si="1"/>
-        <v>122</v>
-      </c>
-      <c r="B122" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A122,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>4715.0214909170891</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A123">
-        <f t="shared" si="1"/>
-        <v>123</v>
-      </c>
-      <c r="B123" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A123,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>4755.9950946565823</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A124">
-        <f t="shared" si="1"/>
-        <v>124</v>
-      </c>
-      <c r="B124" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A124,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>4796.9686983960764</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A125">
-        <f t="shared" si="1"/>
-        <v>125</v>
-      </c>
-      <c r="B125" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A125,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>4837.9423021355706</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A126">
-        <f t="shared" si="1"/>
-        <v>126</v>
-      </c>
-      <c r="B126" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A126,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>4878.9159058750647</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A127">
-        <f t="shared" si="1"/>
-        <v>127</v>
-      </c>
-      <c r="B127" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A127,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>4919.8895096145579</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A128">
-        <f t="shared" si="1"/>
-        <v>128</v>
-      </c>
-      <c r="B128" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A128,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>4960.8631133540521</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A129">
-        <f t="shared" si="1"/>
-        <v>129</v>
-      </c>
-      <c r="B129" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A129,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>5001.8367170935462</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A130">
-        <f t="shared" si="1"/>
-        <v>130</v>
-      </c>
-      <c r="B130" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A130,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>5042.8103208330394</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A131">
-        <f t="shared" ref="A131:A194" si="2">A130+1</f>
-        <v>131</v>
-      </c>
-      <c r="B131" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A131,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>5083.7839245725336</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A132">
-        <f t="shared" si="2"/>
-        <v>132</v>
-      </c>
-      <c r="B132" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A132,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>5124.7575283120277</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A133">
-        <f t="shared" si="2"/>
-        <v>133</v>
-      </c>
-      <c r="B133" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A133,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>5165.7311320515219</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A134">
-        <f t="shared" si="2"/>
-        <v>134</v>
-      </c>
-      <c r="B134" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A134,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>5206.7047357910151</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A135">
-        <f t="shared" si="2"/>
-        <v>135</v>
-      </c>
-      <c r="B135" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A135,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>5247.6783395305092</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A136">
-        <f t="shared" si="2"/>
-        <v>136</v>
-      </c>
-      <c r="B136" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A136,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>5288.6519432700034</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A137">
-        <f t="shared" si="2"/>
-        <v>137</v>
-      </c>
-      <c r="B137" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A137,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>5329.6255470094975</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A138">
-        <f t="shared" si="2"/>
-        <v>138</v>
-      </c>
-      <c r="B138" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A138,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>5370.5991507489907</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A139">
-        <f t="shared" si="2"/>
-        <v>139</v>
-      </c>
-      <c r="B139" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A139,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>5411.5727544884849</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A140">
-        <f t="shared" si="2"/>
-        <v>140</v>
-      </c>
-      <c r="B140" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A140,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>5452.546358227979</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A141">
-        <f t="shared" si="2"/>
-        <v>141</v>
-      </c>
-      <c r="B141" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A141,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>5493.5199619674731</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A142">
-        <f t="shared" si="2"/>
-        <v>142</v>
-      </c>
-      <c r="B142" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A142,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>5534.4935657069664</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A143">
-        <f t="shared" si="2"/>
-        <v>143</v>
-      </c>
-      <c r="B143" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A143,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>5575.4671694464605</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A144">
-        <f t="shared" si="2"/>
-        <v>144</v>
-      </c>
-      <c r="B144" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A144,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>5616.4407731859546</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A145">
-        <f t="shared" si="2"/>
-        <v>145</v>
-      </c>
-      <c r="B145" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A145,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>5657.4143769254488</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A146">
-        <f t="shared" si="2"/>
-        <v>146</v>
-      </c>
-      <c r="B146" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A146,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>5698.387980664942</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A147">
-        <f t="shared" si="2"/>
-        <v>147</v>
-      </c>
-      <c r="B147" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A147,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>5739.3615844044361</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A148">
-        <f t="shared" si="2"/>
-        <v>148</v>
-      </c>
-      <c r="B148" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A148,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>5780.3351881439303</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A149">
-        <f t="shared" si="2"/>
-        <v>149</v>
-      </c>
-      <c r="B149" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A149,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>5821.3087918834244</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A150">
-        <f t="shared" si="2"/>
-        <v>150</v>
-      </c>
-      <c r="B150" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A150,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>5862.2823956229176</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A151">
-        <f t="shared" si="2"/>
-        <v>151</v>
-      </c>
-      <c r="B151" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A151,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>5903.2559993624118</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A152">
-        <f t="shared" si="2"/>
-        <v>152</v>
-      </c>
-      <c r="B152" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A152,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>5944.2296031019059</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A153">
-        <f t="shared" si="2"/>
-        <v>153</v>
-      </c>
-      <c r="B153" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A153,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>5985.2032068414001</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A154">
-        <f t="shared" si="2"/>
-        <v>154</v>
-      </c>
-      <c r="B154" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A154,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>6026.1768105808933</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A155">
-        <f t="shared" si="2"/>
-        <v>155</v>
-      </c>
-      <c r="B155" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A155,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>6067.1504143203874</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A156">
-        <f t="shared" si="2"/>
-        <v>156</v>
-      </c>
-      <c r="B156" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A156,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>6108.1240180598816</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A157">
-        <f t="shared" si="2"/>
-        <v>157</v>
-      </c>
-      <c r="B157" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A157,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>6149.0976217993757</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A158">
-        <f t="shared" si="2"/>
-        <v>158</v>
-      </c>
-      <c r="B158" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A158,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>6190.0712255388689</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A159">
-        <f t="shared" si="2"/>
-        <v>159</v>
-      </c>
-      <c r="B159" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A159,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>6231.0448292783631</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A160">
-        <f t="shared" si="2"/>
-        <v>160</v>
-      </c>
-      <c r="B160" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A160,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>6272.0184330178572</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A161">
-        <f t="shared" si="2"/>
-        <v>161</v>
-      </c>
-      <c r="B161" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A161,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>6312.9920367573504</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A162">
-        <f t="shared" si="2"/>
-        <v>162</v>
-      </c>
-      <c r="B162" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A162,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>6353.9656404968446</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A163">
-        <f t="shared" si="2"/>
-        <v>163</v>
-      </c>
-      <c r="B163" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A163,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>6394.9392442363387</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A164">
-        <f t="shared" si="2"/>
-        <v>164</v>
-      </c>
-      <c r="B164" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A164,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>6435.9128479758328</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A165">
-        <f t="shared" si="2"/>
-        <v>165</v>
-      </c>
-      <c r="B165" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A165,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>6476.8864517153261</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A166">
-        <f t="shared" si="2"/>
-        <v>166</v>
-      </c>
-      <c r="B166" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A166,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>6517.8600554548202</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A167">
-        <f t="shared" si="2"/>
-        <v>167</v>
-      </c>
-      <c r="B167" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A167,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>6558.8336591943144</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A168">
-        <f t="shared" si="2"/>
-        <v>168</v>
-      </c>
-      <c r="B168" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A168,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>6599.8072629338085</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A169">
-        <f t="shared" si="2"/>
-        <v>169</v>
-      </c>
-      <c r="B169" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A169,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>6640.7808666733017</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A170">
-        <f t="shared" si="2"/>
-        <v>170</v>
-      </c>
-      <c r="B170" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A170,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>6681.7544704127959</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A171">
-        <f t="shared" si="2"/>
-        <v>171</v>
-      </c>
-      <c r="B171" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A171,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>6722.72807415229</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A172">
-        <f t="shared" si="2"/>
-        <v>172</v>
-      </c>
-      <c r="B172" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A172,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>6763.7016778917841</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A173">
-        <f t="shared" si="2"/>
-        <v>173</v>
-      </c>
-      <c r="B173" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A173,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>6804.6752816312774</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A174">
-        <f t="shared" si="2"/>
-        <v>174</v>
-      </c>
-      <c r="B174" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A174,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>6845.6488853707715</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A175">
-        <f t="shared" si="2"/>
-        <v>175</v>
-      </c>
-      <c r="B175" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A175,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>6886.6224891102656</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A176">
-        <f t="shared" si="2"/>
-        <v>176</v>
-      </c>
-      <c r="B176" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A176,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>6927.5960928497598</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A177">
-        <f t="shared" si="2"/>
-        <v>177</v>
-      </c>
-      <c r="B177" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A177,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>6968.569696589253</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A178">
-        <f t="shared" si="2"/>
-        <v>178</v>
-      </c>
-      <c r="B178" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A178,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>7009.5433003287471</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A179">
-        <f t="shared" si="2"/>
-        <v>179</v>
-      </c>
-      <c r="B179" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A179,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>7050.5169040682413</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A180">
-        <f t="shared" si="2"/>
-        <v>180</v>
-      </c>
-      <c r="B180" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A180,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>7091.4905078077354</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A181">
-        <f t="shared" si="2"/>
-        <v>181</v>
-      </c>
-      <c r="B181" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A181,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>7132.4641115472286</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A182">
-        <f t="shared" si="2"/>
-        <v>182</v>
-      </c>
-      <c r="B182" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A182,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>7173.4377152867228</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A183">
-        <f t="shared" si="2"/>
-        <v>183</v>
-      </c>
-      <c r="B183" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A183,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>7214.4113190262169</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A184">
-        <f t="shared" si="2"/>
-        <v>184</v>
-      </c>
-      <c r="B184" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A184,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>7255.3849227657111</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A185">
-        <f t="shared" si="2"/>
-        <v>185</v>
-      </c>
-      <c r="B185" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A185,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>7296.3585265052043</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A186">
-        <f t="shared" si="2"/>
-        <v>186</v>
-      </c>
-      <c r="B186" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A186,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>7337.3321302446984</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A187">
-        <f t="shared" si="2"/>
-        <v>187</v>
-      </c>
-      <c r="B187" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A187,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>7378.3057339841926</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A188">
-        <f t="shared" si="2"/>
-        <v>188</v>
-      </c>
-      <c r="B188" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A188,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>7419.2793377236867</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A189">
-        <f t="shared" si="2"/>
-        <v>189</v>
-      </c>
-      <c r="B189" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A189,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>7460.2529414631799</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A190">
-        <f t="shared" si="2"/>
-        <v>190</v>
-      </c>
-      <c r="B190" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A190,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>7501.2265452026741</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A191">
-        <f t="shared" si="2"/>
-        <v>191</v>
-      </c>
-      <c r="B191" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A191,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>7542.2001489421682</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A192">
-        <f t="shared" si="2"/>
-        <v>192</v>
-      </c>
-      <c r="B192" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A192,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>7583.1737526816614</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A193">
-        <f t="shared" si="2"/>
-        <v>193</v>
-      </c>
-      <c r="B193" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A193,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>7624.1473564211556</v>
-      </c>
-    </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A194">
-        <f t="shared" si="2"/>
-        <v>194</v>
-      </c>
-      <c r="B194" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A194,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>7665.1209601606497</v>
-      </c>
-    </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A195">
-        <f t="shared" ref="A195:A258" si="3">A194+1</f>
-        <v>195</v>
-      </c>
-      <c r="B195" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A195,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>7706.0945639001438</v>
-      </c>
-    </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A196">
-        <f t="shared" si="3"/>
-        <v>196</v>
-      </c>
-      <c r="B196" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A196,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>7747.0681676396371</v>
-      </c>
-    </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A197">
-        <f t="shared" si="3"/>
-        <v>197</v>
-      </c>
-      <c r="B197" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A197,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>7788.0417713791312</v>
-      </c>
-    </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A198">
-        <f t="shared" si="3"/>
-        <v>198</v>
-      </c>
-      <c r="B198" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A198,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>7829.0153751186253</v>
-      </c>
-    </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A199">
-        <f t="shared" si="3"/>
-        <v>199</v>
-      </c>
-      <c r="B199" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A199,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>7869.9889788581195</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A200">
-        <f t="shared" si="3"/>
-        <v>200</v>
-      </c>
-      <c r="B200" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A200,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>7910.9625825976127</v>
-      </c>
-    </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A201">
-        <f t="shared" si="3"/>
-        <v>201</v>
-      </c>
-      <c r="B201" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A201,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>7951.9361863371068</v>
-      </c>
-    </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A202">
-        <f t="shared" si="3"/>
-        <v>202</v>
-      </c>
-      <c r="B202" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A202,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>7992.909790076601</v>
-      </c>
-    </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A203">
-        <f t="shared" si="3"/>
-        <v>203</v>
-      </c>
-      <c r="B203" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A203,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>8033.8833938160951</v>
-      </c>
-    </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A204">
-        <f t="shared" si="3"/>
-        <v>204</v>
-      </c>
-      <c r="B204" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A204,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>8074.8569975555893</v>
-      </c>
-    </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A205">
-        <f t="shared" si="3"/>
-        <v>205</v>
-      </c>
-      <c r="B205" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A205,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>8115.8306012950834</v>
-      </c>
-    </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A206">
-        <f t="shared" si="3"/>
-        <v>206</v>
-      </c>
-      <c r="B206" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A206,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>8156.8042050345757</v>
-      </c>
-    </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A207">
-        <f t="shared" si="3"/>
-        <v>207</v>
-      </c>
-      <c r="B207" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A207,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>8197.7778087740699</v>
-      </c>
-    </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A208">
-        <f t="shared" si="3"/>
-        <v>208</v>
-      </c>
-      <c r="B208" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A208,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>8238.751412513564</v>
-      </c>
-    </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A209">
-        <f t="shared" si="3"/>
-        <v>209</v>
-      </c>
-      <c r="B209" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A209,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>8279.7250162530581</v>
-      </c>
-    </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A210">
-        <f t="shared" si="3"/>
-        <v>210</v>
-      </c>
-      <c r="B210" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A210,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>8320.6986199925523</v>
-      </c>
-    </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A211">
-        <f t="shared" si="3"/>
-        <v>211</v>
-      </c>
-      <c r="B211" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A211,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>8361.6722237320464</v>
-      </c>
-    </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A212">
-        <f t="shared" si="3"/>
-        <v>212</v>
-      </c>
-      <c r="B212" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A212,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>8402.6458274715405</v>
-      </c>
-    </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A213">
-        <f t="shared" si="3"/>
-        <v>213</v>
-      </c>
-      <c r="B213" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A213,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>8443.6194312110347</v>
-      </c>
-    </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A214">
-        <f t="shared" si="3"/>
-        <v>214</v>
-      </c>
-      <c r="B214" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A214,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>8484.593034950527</v>
-      </c>
-    </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A215">
-        <f t="shared" si="3"/>
-        <v>215</v>
-      </c>
-      <c r="B215" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A215,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>8525.5666386900211</v>
-      </c>
-    </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A216">
-        <f t="shared" si="3"/>
-        <v>216</v>
-      </c>
-      <c r="B216" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A216,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>8566.5402424295153</v>
-      </c>
-    </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A217">
-        <f t="shared" si="3"/>
-        <v>217</v>
-      </c>
-      <c r="B217" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A217,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>8607.5138461690094</v>
-      </c>
-    </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A218">
-        <f t="shared" si="3"/>
-        <v>218</v>
-      </c>
-      <c r="B218" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A218,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>8648.4874499085035</v>
-      </c>
-    </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A219">
-        <f t="shared" si="3"/>
-        <v>219</v>
-      </c>
-      <c r="B219" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A219,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>8689.4610536479977</v>
-      </c>
-    </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A220">
-        <f t="shared" si="3"/>
-        <v>220</v>
-      </c>
-      <c r="B220" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A220,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>8730.4346573874918</v>
-      </c>
-    </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A221">
-        <f t="shared" si="3"/>
-        <v>221</v>
-      </c>
-      <c r="B221" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A221,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>8771.408261126986</v>
-      </c>
-    </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A222">
-        <f t="shared" si="3"/>
-        <v>222</v>
-      </c>
-      <c r="B222" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A222,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>8812.3818648664783</v>
-      </c>
-    </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A223">
-        <f t="shared" si="3"/>
-        <v>223</v>
-      </c>
-      <c r="B223" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A223,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>8853.3554686059724</v>
-      </c>
-    </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A224">
-        <f t="shared" si="3"/>
-        <v>224</v>
-      </c>
-      <c r="B224" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A224,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>8894.3290723454666</v>
-      </c>
-    </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A225">
-        <f t="shared" si="3"/>
-        <v>225</v>
-      </c>
-      <c r="B225" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A225,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>8935.3026760849607</v>
-      </c>
-    </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A226">
-        <f t="shared" si="3"/>
-        <v>226</v>
-      </c>
-      <c r="B226" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A226,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>8976.2762798244548</v>
-      </c>
-    </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A227">
-        <f t="shared" si="3"/>
-        <v>227</v>
-      </c>
-      <c r="B227" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A227,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>9017.249883563949</v>
-      </c>
-    </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A228">
-        <f t="shared" si="3"/>
-        <v>228</v>
-      </c>
-      <c r="B228" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A228,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>9058.2234873034431</v>
-      </c>
-    </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A229">
-        <f t="shared" si="3"/>
-        <v>229</v>
-      </c>
-      <c r="B229" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A229,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>9099.1970910429354</v>
-      </c>
-    </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A230">
-        <f t="shared" si="3"/>
-        <v>230</v>
-      </c>
-      <c r="B230" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A230,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>9140.1706947824296</v>
-      </c>
-    </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A231">
-        <f t="shared" si="3"/>
-        <v>231</v>
-      </c>
-      <c r="B231" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A231,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>9181.1442985219237</v>
-      </c>
-    </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A232">
-        <f t="shared" si="3"/>
-        <v>232</v>
-      </c>
-      <c r="B232" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A232,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>9222.1179022614178</v>
-      </c>
-    </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A233">
-        <f t="shared" si="3"/>
-        <v>233</v>
-      </c>
-      <c r="B233" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A233,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>9263.091506000912</v>
-      </c>
-    </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A234">
-        <f t="shared" si="3"/>
-        <v>234</v>
-      </c>
-      <c r="B234" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A234,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>9304.0651097404061</v>
-      </c>
-    </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A235">
-        <f t="shared" si="3"/>
-        <v>235</v>
-      </c>
-      <c r="B235" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A235,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>9345.0387134799003</v>
-      </c>
-    </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A236">
-        <f t="shared" si="3"/>
-        <v>236</v>
-      </c>
-      <c r="B236" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A236,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>9386.0123172193944</v>
-      </c>
-    </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A237">
-        <f t="shared" si="3"/>
-        <v>237</v>
-      </c>
-      <c r="B237" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A237,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>9426.9859209588867</v>
-      </c>
-    </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A238">
-        <f t="shared" si="3"/>
-        <v>238</v>
-      </c>
-      <c r="B238" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A238,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>9467.9595246983808</v>
-      </c>
-    </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A239">
-        <f t="shared" si="3"/>
-        <v>239</v>
-      </c>
-      <c r="B239" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A239,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>9508.933128437875</v>
-      </c>
-    </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A240">
-        <f t="shared" si="3"/>
-        <v>240</v>
-      </c>
-      <c r="B240" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A240,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>9549.9067321773691</v>
-      </c>
-    </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A241">
-        <f t="shared" si="3"/>
-        <v>241</v>
-      </c>
-      <c r="B241" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A241,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>9590.8803359168633</v>
-      </c>
-    </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A242">
-        <f t="shared" si="3"/>
-        <v>242</v>
-      </c>
-      <c r="B242" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A242,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>9631.8539396563574</v>
-      </c>
-    </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A243">
-        <f t="shared" si="3"/>
-        <v>243</v>
-      </c>
-      <c r="B243" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A243,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>9672.8275433958515</v>
-      </c>
-    </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A244">
-        <f t="shared" si="3"/>
-        <v>244</v>
-      </c>
-      <c r="B244" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A244,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>9713.8011471353457</v>
-      </c>
-    </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A245">
-        <f t="shared" si="3"/>
-        <v>245</v>
-      </c>
-      <c r="B245" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A245,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>9754.774750874838</v>
-      </c>
-    </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A246">
-        <f t="shared" si="3"/>
-        <v>246</v>
-      </c>
-      <c r="B246" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A246,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>9795.7483546143321</v>
-      </c>
-    </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A247">
-        <f t="shared" si="3"/>
-        <v>247</v>
-      </c>
-      <c r="B247" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A247,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>9836.7219583538263</v>
-      </c>
-    </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A248">
-        <f t="shared" si="3"/>
-        <v>248</v>
-      </c>
-      <c r="B248" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A248,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>9877.6955620933204</v>
-      </c>
-    </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A249">
-        <f t="shared" si="3"/>
-        <v>249</v>
-      </c>
-      <c r="B249" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A249,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>9918.6691658328145</v>
-      </c>
-    </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A250">
-        <f t="shared" si="3"/>
-        <v>250</v>
-      </c>
-      <c r="B250" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A250,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>9959.6427695723087</v>
-      </c>
-    </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A251">
-        <f t="shared" si="3"/>
-        <v>251</v>
-      </c>
-      <c r="B251" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A251,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>10000.616373311803</v>
-      </c>
-    </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A252">
-        <f t="shared" si="3"/>
-        <v>252</v>
-      </c>
-      <c r="B252" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A252,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>10041.589977051297</v>
-      </c>
-    </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A253">
-        <f t="shared" si="3"/>
-        <v>253</v>
-      </c>
-      <c r="B253" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A253,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>10082.563580790789</v>
-      </c>
-    </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A254">
-        <f t="shared" si="3"/>
-        <v>254</v>
-      </c>
-      <c r="B254" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A254,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>10123.537184530283</v>
-      </c>
-    </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A255">
-        <f t="shared" si="3"/>
-        <v>255</v>
-      </c>
-      <c r="B255" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A255,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>10164.510788269778</v>
-      </c>
-    </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A256">
-        <f t="shared" si="3"/>
-        <v>256</v>
-      </c>
-      <c r="B256" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A256,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>10205.484392009272</v>
-      </c>
-    </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A257">
-        <f t="shared" si="3"/>
-        <v>257</v>
-      </c>
-      <c r="B257" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A257,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>10246.457995748766</v>
-      </c>
-    </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A258">
-        <f t="shared" si="3"/>
-        <v>258</v>
-      </c>
-      <c r="B258" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A258,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>10287.43159948826</v>
-      </c>
-    </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A259">
-        <f t="shared" ref="A259:A322" si="4">A258+1</f>
-        <v>259</v>
-      </c>
-      <c r="B259" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A259,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>10328.405203227754</v>
-      </c>
-    </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A260">
-        <f t="shared" si="4"/>
-        <v>260</v>
-      </c>
-      <c r="B260" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A260,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>10369.378806967246</v>
-      </c>
-    </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A261">
-        <f t="shared" si="4"/>
-        <v>261</v>
-      </c>
-      <c r="B261" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A261,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>10410.352410706741</v>
-      </c>
-    </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A262">
-        <f t="shared" si="4"/>
-        <v>262</v>
-      </c>
-      <c r="B262" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A262,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>10451.326014446235</v>
-      </c>
-    </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A263">
-        <f t="shared" si="4"/>
-        <v>263</v>
-      </c>
-      <c r="B263" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A263,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>10492.299618185729</v>
-      </c>
-    </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A264">
-        <f t="shared" si="4"/>
-        <v>264</v>
-      </c>
-      <c r="B264" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A264,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>10533.273221925223</v>
-      </c>
-    </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A265">
-        <f t="shared" si="4"/>
-        <v>265</v>
-      </c>
-      <c r="B265" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A265,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>10574.246825664717</v>
-      </c>
-    </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A266">
-        <f t="shared" si="4"/>
-        <v>266</v>
-      </c>
-      <c r="B266" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A266,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>10615.220429404211</v>
-      </c>
-    </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A267">
-        <f t="shared" si="4"/>
-        <v>267</v>
-      </c>
-      <c r="B267" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A267,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>10656.194033143705</v>
-      </c>
-    </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A268">
-        <f t="shared" si="4"/>
-        <v>268</v>
-      </c>
-      <c r="B268" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A268,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>10697.167636883198</v>
-      </c>
-    </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A269">
-        <f t="shared" si="4"/>
-        <v>269</v>
-      </c>
-      <c r="B269" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A269,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>10738.141240622692</v>
-      </c>
-    </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A270">
-        <f t="shared" si="4"/>
-        <v>270</v>
-      </c>
-      <c r="B270" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A270,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>10779.114844362186</v>
-      </c>
-    </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A271">
-        <f t="shared" si="4"/>
-        <v>271</v>
-      </c>
-      <c r="B271" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A271,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>10820.08844810168</v>
-      </c>
-    </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A272">
-        <f t="shared" si="4"/>
-        <v>272</v>
-      </c>
-      <c r="B272" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A272,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>10861.062051841174</v>
-      </c>
-    </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A273">
-        <f t="shared" si="4"/>
-        <v>273</v>
-      </c>
-      <c r="B273" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A273,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>10902.035655580668</v>
-      </c>
-    </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A274">
-        <f t="shared" si="4"/>
-        <v>274</v>
-      </c>
-      <c r="B274" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A274,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>10943.009259320163</v>
-      </c>
-    </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A275">
-        <f t="shared" si="4"/>
-        <v>275</v>
-      </c>
-      <c r="B275" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A275,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>10983.982863059657</v>
-      </c>
-    </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A276">
-        <f t="shared" si="4"/>
-        <v>276</v>
-      </c>
-      <c r="B276" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A276,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>11024.956466799149</v>
-      </c>
-    </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A277">
-        <f t="shared" si="4"/>
-        <v>277</v>
-      </c>
-      <c r="B277" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A277,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>11065.930070538643</v>
-      </c>
-    </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A278">
-        <f t="shared" si="4"/>
-        <v>278</v>
-      </c>
-      <c r="B278" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A278,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>11106.903674278137</v>
-      </c>
-    </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A279">
-        <f t="shared" si="4"/>
-        <v>279</v>
-      </c>
-      <c r="B279" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A279,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>11147.877278017631</v>
-      </c>
-    </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A280">
-        <f t="shared" si="4"/>
-        <v>280</v>
-      </c>
-      <c r="B280" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A280,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>11188.850881757126</v>
-      </c>
-    </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A281">
-        <f t="shared" si="4"/>
-        <v>281</v>
-      </c>
-      <c r="B281" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A281,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>11229.82448549662</v>
-      </c>
-    </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A282">
-        <f t="shared" si="4"/>
-        <v>282</v>
-      </c>
-      <c r="B282" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A282,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>11270.798089236114</v>
-      </c>
-    </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A283">
-        <f t="shared" si="4"/>
-        <v>283</v>
-      </c>
-      <c r="B283" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A283,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>11311.771692975608</v>
-      </c>
-    </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A284">
-        <f t="shared" si="4"/>
-        <v>284</v>
-      </c>
-      <c r="B284" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A284,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>11352.7452967151</v>
-      </c>
-    </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A285">
-        <f t="shared" si="4"/>
-        <v>285</v>
-      </c>
-      <c r="B285" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A285,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>11393.718900454594</v>
-      </c>
-    </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A286">
-        <f t="shared" si="4"/>
-        <v>286</v>
-      </c>
-      <c r="B286" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A286,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>11434.692504194089</v>
-      </c>
-    </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A287">
-        <f t="shared" si="4"/>
-        <v>287</v>
-      </c>
-      <c r="B287" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A287,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>11475.666107933583</v>
-      </c>
-    </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A288">
-        <f t="shared" si="4"/>
-        <v>288</v>
-      </c>
-      <c r="B288" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A288,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>11516.639711673077</v>
-      </c>
-    </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A289">
-        <f t="shared" si="4"/>
-        <v>289</v>
-      </c>
-      <c r="B289" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A289,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>11557.613315412571</v>
-      </c>
-    </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A290">
-        <f t="shared" si="4"/>
-        <v>290</v>
-      </c>
-      <c r="B290" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A290,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>11598.586919152065</v>
-      </c>
-    </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A291">
-        <f t="shared" si="4"/>
-        <v>291</v>
-      </c>
-      <c r="B291" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A291,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>11639.560522891557</v>
-      </c>
-    </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A292">
-        <f t="shared" si="4"/>
-        <v>292</v>
-      </c>
-      <c r="B292" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A292,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>11680.534126631052</v>
-      </c>
-    </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A293">
-        <f t="shared" si="4"/>
-        <v>293</v>
-      </c>
-      <c r="B293" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A293,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>11721.507730370546</v>
-      </c>
-    </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A294">
-        <f t="shared" si="4"/>
-        <v>294</v>
-      </c>
-      <c r="B294" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A294,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>11762.48133411004</v>
-      </c>
-    </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A295">
-        <f t="shared" si="4"/>
-        <v>295</v>
-      </c>
-      <c r="B295" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A295,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>11803.454937849534</v>
-      </c>
-    </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A296">
-        <f t="shared" si="4"/>
-        <v>296</v>
-      </c>
-      <c r="B296" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A296,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>11844.428541589028</v>
-      </c>
-    </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A297">
-        <f t="shared" si="4"/>
-        <v>297</v>
-      </c>
-      <c r="B297" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A297,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>11885.402145328522</v>
-      </c>
-    </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A298">
-        <f t="shared" si="4"/>
-        <v>298</v>
-      </c>
-      <c r="B298" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A298,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>11926.375749068016</v>
-      </c>
-    </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A299">
-        <f t="shared" si="4"/>
-        <v>299</v>
-      </c>
-      <c r="B299" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A299,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>11967.349352807509</v>
-      </c>
-    </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A300">
-        <f t="shared" si="4"/>
-        <v>300</v>
-      </c>
-      <c r="B300" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A300,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>12008.322956547003</v>
-      </c>
-    </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A301">
-        <f t="shared" si="4"/>
-        <v>301</v>
-      </c>
-      <c r="B301" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A301,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>12049.296560286497</v>
-      </c>
-    </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A302">
-        <f t="shared" si="4"/>
-        <v>302</v>
-      </c>
-      <c r="B302" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A302,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>12090.270164025991</v>
-      </c>
-    </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A303">
-        <f t="shared" si="4"/>
-        <v>303</v>
-      </c>
-      <c r="B303" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A303,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>12131.243767765485</v>
-      </c>
-    </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A304">
-        <f t="shared" si="4"/>
-        <v>304</v>
-      </c>
-      <c r="B304" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A304,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>12172.217371504979</v>
-      </c>
-    </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A305">
-        <f t="shared" si="4"/>
-        <v>305</v>
-      </c>
-      <c r="B305" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A305,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>12213.190975244474</v>
-      </c>
-    </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A306">
-        <f t="shared" si="4"/>
-        <v>306</v>
-      </c>
-      <c r="B306" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A306,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>12254.164578983968</v>
-      </c>
-    </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A307">
-        <f t="shared" si="4"/>
-        <v>307</v>
-      </c>
-      <c r="B307" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A307,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>12295.13818272346</v>
-      </c>
-    </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A308">
-        <f t="shared" si="4"/>
-        <v>308</v>
-      </c>
-      <c r="B308" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A308,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>12336.111786462954</v>
-      </c>
-    </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A309">
-        <f t="shared" si="4"/>
-        <v>309</v>
-      </c>
-      <c r="B309" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A309,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>12377.085390202448</v>
-      </c>
-    </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A310">
-        <f t="shared" si="4"/>
-        <v>310</v>
-      </c>
-      <c r="B310" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A310,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>12418.058993941942</v>
-      </c>
-    </row>
-    <row r="311" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A311">
-        <f t="shared" si="4"/>
-        <v>311</v>
-      </c>
-      <c r="B311" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A311,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>12459.032597681437</v>
-      </c>
-    </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A312">
-        <f t="shared" si="4"/>
-        <v>312</v>
-      </c>
-      <c r="B312" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A312,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>12500.006201420931</v>
-      </c>
-    </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A313">
-        <f t="shared" si="4"/>
-        <v>313</v>
-      </c>
-      <c r="B313" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A313,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>12540.979805160425</v>
-      </c>
-    </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A314">
-        <f t="shared" si="4"/>
-        <v>314</v>
-      </c>
-      <c r="B314" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A314,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>12581.953408899919</v>
-      </c>
-    </row>
-    <row r="315" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A315">
-        <f t="shared" si="4"/>
-        <v>315</v>
-      </c>
-      <c r="B315" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A315,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>12622.927012639411</v>
-      </c>
-    </row>
-    <row r="316" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A316">
-        <f t="shared" si="4"/>
-        <v>316</v>
-      </c>
-      <c r="B316" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A316,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>12663.900616378905</v>
-      </c>
-    </row>
-    <row r="317" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A317">
-        <f t="shared" si="4"/>
-        <v>317</v>
-      </c>
-      <c r="B317" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A317,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>12704.8742201184</v>
-      </c>
-    </row>
-    <row r="318" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A318">
-        <f t="shared" si="4"/>
-        <v>318</v>
-      </c>
-      <c r="B318" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A318,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>12745.847823857894</v>
-      </c>
-    </row>
-    <row r="319" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A319">
-        <f t="shared" si="4"/>
-        <v>319</v>
-      </c>
-      <c r="B319" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A319,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>12786.821427597388</v>
-      </c>
-    </row>
-    <row r="320" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A320">
-        <f t="shared" si="4"/>
-        <v>320</v>
-      </c>
-      <c r="B320" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A320,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>12827.795031336882</v>
-      </c>
-    </row>
-    <row r="321" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A321">
-        <f t="shared" si="4"/>
-        <v>321</v>
-      </c>
-      <c r="B321" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A321,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>12868.768635076376</v>
-      </c>
-    </row>
-    <row r="322" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A322">
-        <f t="shared" si="4"/>
-        <v>322</v>
-      </c>
-      <c r="B322" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A322,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>12909.742238815868</v>
-      </c>
-    </row>
-    <row r="323" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A323">
-        <f t="shared" ref="A323:A386" si="5">A322+1</f>
-        <v>323</v>
-      </c>
-      <c r="B323" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A323,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>12950.715842555363</v>
-      </c>
-    </row>
-    <row r="324" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A324">
-        <f t="shared" si="5"/>
-        <v>324</v>
-      </c>
-      <c r="B324" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A324,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>12991.689446294857</v>
-      </c>
-    </row>
-    <row r="325" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A325">
-        <f t="shared" si="5"/>
-        <v>325</v>
-      </c>
-      <c r="B325" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A325,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>13032.663050034351</v>
-      </c>
-    </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A326">
-        <f t="shared" si="5"/>
-        <v>326</v>
-      </c>
-      <c r="B326" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A326,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>13073.636653773845</v>
-      </c>
-    </row>
-    <row r="327" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A327">
-        <f t="shared" si="5"/>
-        <v>327</v>
-      </c>
-      <c r="B327" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A327,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>13114.610257513339</v>
-      </c>
-    </row>
-    <row r="328" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A328">
-        <f t="shared" si="5"/>
-        <v>328</v>
-      </c>
-      <c r="B328" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A328,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>13155.583861252833</v>
-      </c>
-    </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A329">
-        <f t="shared" si="5"/>
-        <v>329</v>
-      </c>
-      <c r="B329" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A329,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>13196.557464992327</v>
-      </c>
-    </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A330">
-        <f t="shared" si="5"/>
-        <v>330</v>
-      </c>
-      <c r="B330" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A330,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>13237.53106873182</v>
-      </c>
-    </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A331">
-        <f t="shared" si="5"/>
-        <v>331</v>
-      </c>
-      <c r="B331" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A331,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>13278.504672471314</v>
-      </c>
-    </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A332">
-        <f t="shared" si="5"/>
-        <v>332</v>
-      </c>
-      <c r="B332" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A332,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>13319.478276210808</v>
-      </c>
-    </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A333">
-        <f t="shared" si="5"/>
-        <v>333</v>
-      </c>
-      <c r="B333" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A333,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>13360.451879950302</v>
-      </c>
-    </row>
-    <row r="334" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A334">
-        <f t="shared" si="5"/>
-        <v>334</v>
-      </c>
-      <c r="B334" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A334,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>13401.425483689796</v>
-      </c>
-    </row>
-    <row r="335" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A335">
-        <f t="shared" si="5"/>
-        <v>335</v>
-      </c>
-      <c r="B335" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A335,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>13442.39908742929</v>
-      </c>
-    </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A336">
-        <f t="shared" si="5"/>
-        <v>336</v>
-      </c>
-      <c r="B336" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A336,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>13483.372691168785</v>
-      </c>
-    </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A337">
-        <f t="shared" si="5"/>
-        <v>337</v>
-      </c>
-      <c r="B337" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A337,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>13524.346294908279</v>
-      </c>
-    </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A338">
-        <f t="shared" si="5"/>
-        <v>338</v>
-      </c>
-      <c r="B338" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A338,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>13565.319898647771</v>
-      </c>
-    </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A339">
-        <f t="shared" si="5"/>
-        <v>339</v>
-      </c>
-      <c r="B339" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A339,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>13606.293502387265</v>
-      </c>
-    </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A340">
-        <f t="shared" si="5"/>
-        <v>340</v>
-      </c>
-      <c r="B340" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A340,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>13647.267106126759</v>
-      </c>
-    </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A341">
-        <f t="shared" si="5"/>
-        <v>341</v>
-      </c>
-      <c r="B341" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A341,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>13688.240709866253</v>
-      </c>
-    </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A342">
-        <f t="shared" si="5"/>
-        <v>342</v>
-      </c>
-      <c r="B342" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A342,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>13729.214313605748</v>
-      </c>
-    </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A343">
-        <f t="shared" si="5"/>
-        <v>343</v>
-      </c>
-      <c r="B343" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A343,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>13770.187917345242</v>
-      </c>
-    </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A344">
-        <f t="shared" si="5"/>
-        <v>344</v>
-      </c>
-      <c r="B344" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A344,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>13811.161521084736</v>
-      </c>
-    </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A345">
-        <f t="shared" si="5"/>
-        <v>345</v>
-      </c>
-      <c r="B345" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A345,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>13852.13512482423</v>
-      </c>
-    </row>
-    <row r="346" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A346">
-        <f t="shared" si="5"/>
-        <v>346</v>
-      </c>
-      <c r="B346" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A346,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>13893.108728563722</v>
-      </c>
-    </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A347">
-        <f t="shared" si="5"/>
-        <v>347</v>
-      </c>
-      <c r="B347" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A347,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>13934.082332303216</v>
-      </c>
-    </row>
-    <row r="348" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A348">
-        <f t="shared" si="5"/>
-        <v>348</v>
-      </c>
-      <c r="B348" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A348,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>13975.055936042711</v>
-      </c>
-    </row>
-    <row r="349" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A349">
-        <f t="shared" si="5"/>
-        <v>349</v>
-      </c>
-      <c r="B349" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A349,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>14016.029539782205</v>
-      </c>
-    </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A350">
-        <f t="shared" si="5"/>
-        <v>350</v>
-      </c>
-      <c r="B350" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A350,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>14057.003143521699</v>
-      </c>
-    </row>
-    <row r="351" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A351">
-        <f t="shared" si="5"/>
-        <v>351</v>
-      </c>
-      <c r="B351" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A351,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>14097.976747261193</v>
-      </c>
-    </row>
-    <row r="352" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A352">
-        <f t="shared" si="5"/>
-        <v>352</v>
-      </c>
-      <c r="B352" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A352,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>14138.950351000687</v>
-      </c>
-    </row>
-    <row r="353" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A353">
-        <f t="shared" si="5"/>
-        <v>353</v>
-      </c>
-      <c r="B353" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A353,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>14179.923954740179</v>
-      </c>
-    </row>
-    <row r="354" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A354">
-        <f t="shared" si="5"/>
-        <v>354</v>
-      </c>
-      <c r="B354" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A354,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>14220.897558479674</v>
-      </c>
-    </row>
-    <row r="355" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A355">
-        <f t="shared" si="5"/>
-        <v>355</v>
-      </c>
-      <c r="B355" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A355,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>14261.871162219168</v>
-      </c>
-    </row>
-    <row r="356" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A356">
-        <f t="shared" si="5"/>
-        <v>356</v>
-      </c>
-      <c r="B356" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A356,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>14302.844765958662</v>
-      </c>
-    </row>
-    <row r="357" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A357">
-        <f t="shared" si="5"/>
-        <v>357</v>
-      </c>
-      <c r="B357" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A357,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>14343.818369698156</v>
-      </c>
-    </row>
-    <row r="358" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A358">
-        <f t="shared" si="5"/>
-        <v>358</v>
-      </c>
-      <c r="B358" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A358,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>14384.79197343765</v>
-      </c>
-    </row>
-    <row r="359" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A359">
-        <f t="shared" si="5"/>
-        <v>359</v>
-      </c>
-      <c r="B359" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A359,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>14425.765577177144</v>
-      </c>
-    </row>
-    <row r="360" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A360">
-        <f t="shared" si="5"/>
-        <v>360</v>
-      </c>
-      <c r="B360" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A360,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>14466.739180916638</v>
-      </c>
-    </row>
-    <row r="361" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A361">
-        <f t="shared" si="5"/>
-        <v>361</v>
-      </c>
-      <c r="B361" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A361,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>14507.712784656131</v>
-      </c>
-    </row>
-    <row r="362" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A362">
-        <f t="shared" si="5"/>
-        <v>362</v>
-      </c>
-      <c r="B362" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A362,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>14548.686388395625</v>
-      </c>
-    </row>
-    <row r="363" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A363">
-        <f t="shared" si="5"/>
-        <v>363</v>
-      </c>
-      <c r="B363" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A363,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>14589.659992135119</v>
-      </c>
-    </row>
-    <row r="364" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A364">
-        <f t="shared" si="5"/>
-        <v>364</v>
-      </c>
-      <c r="B364" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A364,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>14630.633595874613</v>
-      </c>
-    </row>
-    <row r="365" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A365">
-        <f t="shared" si="5"/>
-        <v>365</v>
-      </c>
-      <c r="B365" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A365,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>14671.607199614107</v>
-      </c>
-    </row>
-    <row r="366" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A366">
-        <f t="shared" si="5"/>
-        <v>366</v>
-      </c>
-      <c r="B366" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A366,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>14712.580803353601</v>
-      </c>
-    </row>
-    <row r="367" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A367">
-        <f t="shared" si="5"/>
-        <v>367</v>
-      </c>
-      <c r="B367" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A367,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>14753.554407093096</v>
-      </c>
-    </row>
-    <row r="368" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A368">
-        <f t="shared" si="5"/>
-        <v>368</v>
-      </c>
-      <c r="B368" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A368,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>14794.52801083259</v>
-      </c>
-    </row>
-    <row r="369" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A369">
-        <f t="shared" si="5"/>
-        <v>369</v>
-      </c>
-      <c r="B369" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A369,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>14835.501614572082</v>
-      </c>
-    </row>
-    <row r="370" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A370">
-        <f t="shared" si="5"/>
-        <v>370</v>
-      </c>
-      <c r="B370" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A370,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>14876.475218311576</v>
-      </c>
-    </row>
-    <row r="371" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A371">
-        <f t="shared" si="5"/>
-        <v>371</v>
-      </c>
-      <c r="B371" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A371,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>14917.44882205107</v>
-      </c>
-    </row>
-    <row r="372" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A372">
-        <f t="shared" si="5"/>
-        <v>372</v>
-      </c>
-      <c r="B372" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A372,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>14958.422425790564</v>
-      </c>
-    </row>
-    <row r="373" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A373">
-        <f t="shared" si="5"/>
-        <v>373</v>
-      </c>
-      <c r="B373" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A373,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>14999.396029530059</v>
-      </c>
-    </row>
-    <row r="374" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A374">
-        <f t="shared" si="5"/>
-        <v>374</v>
-      </c>
-      <c r="B374" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A374,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>15040.369633269553</v>
-      </c>
-    </row>
-    <row r="375" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A375">
-        <f t="shared" si="5"/>
-        <v>375</v>
-      </c>
-      <c r="B375" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A375,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>15081.343237009047</v>
-      </c>
-    </row>
-    <row r="376" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A376">
-        <f t="shared" si="5"/>
-        <v>376</v>
-      </c>
-      <c r="B376" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A376,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>15122.316840748541</v>
-      </c>
-    </row>
-    <row r="377" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A377">
-        <f t="shared" si="5"/>
-        <v>377</v>
-      </c>
-      <c r="B377" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A377,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>15163.290444488033</v>
-      </c>
-    </row>
-    <row r="378" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A378">
-        <f t="shared" si="5"/>
-        <v>378</v>
-      </c>
-      <c r="B378" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A378,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>15204.264048227527</v>
-      </c>
-    </row>
-    <row r="379" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A379">
-        <f t="shared" si="5"/>
-        <v>379</v>
-      </c>
-      <c r="B379" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A379,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>15245.237651967022</v>
-      </c>
-    </row>
-    <row r="380" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A380">
-        <f t="shared" si="5"/>
-        <v>380</v>
-      </c>
-      <c r="B380" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A380,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>15286.211255706516</v>
-      </c>
-    </row>
-    <row r="381" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A381">
-        <f t="shared" si="5"/>
-        <v>381</v>
-      </c>
-      <c r="B381" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A381,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>15327.18485944601</v>
-      </c>
-    </row>
-    <row r="382" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A382">
-        <f t="shared" si="5"/>
-        <v>382</v>
-      </c>
-      <c r="B382" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A382,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>15368.158463185504</v>
-      </c>
-    </row>
-    <row r="383" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A383">
-        <f t="shared" si="5"/>
-        <v>383</v>
-      </c>
-      <c r="B383" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A383,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>15409.132066924998</v>
-      </c>
-    </row>
-    <row r="384" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A384">
-        <f t="shared" si="5"/>
-        <v>384</v>
-      </c>
-      <c r="B384" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A384,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>15450.10567066449</v>
-      </c>
-    </row>
-    <row r="385" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A385">
-        <f t="shared" si="5"/>
-        <v>385</v>
-      </c>
-      <c r="B385" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A385,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>15491.079274403985</v>
-      </c>
-    </row>
-    <row r="386" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A386">
-        <f t="shared" si="5"/>
-        <v>386</v>
-      </c>
-      <c r="B386" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A386,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>15532.052878143479</v>
-      </c>
-    </row>
-    <row r="387" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A387">
-        <f t="shared" ref="A387:A400" si="6">A386+1</f>
-        <v>387</v>
-      </c>
-      <c r="B387" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A387,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>15573.026481882973</v>
-      </c>
-    </row>
-    <row r="388" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A388">
-        <f t="shared" si="6"/>
-        <v>388</v>
-      </c>
-      <c r="B388" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A388,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>15614.000085622467</v>
-      </c>
-    </row>
-    <row r="389" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A389">
-        <f t="shared" si="6"/>
-        <v>389</v>
-      </c>
-      <c r="B389" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A389,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>15654.973689361961</v>
-      </c>
-    </row>
-    <row r="390" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A390">
-        <f t="shared" si="6"/>
-        <v>390</v>
-      </c>
-      <c r="B390" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A390,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>15695.947293101455</v>
-      </c>
-    </row>
-    <row r="391" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A391">
-        <f t="shared" si="6"/>
-        <v>391</v>
-      </c>
-      <c r="B391" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A391,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>15736.920896840949</v>
-      </c>
-    </row>
-    <row r="392" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A392">
-        <f t="shared" si="6"/>
-        <v>392</v>
-      </c>
-      <c r="B392" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A392,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>15777.894500580442</v>
-      </c>
-    </row>
-    <row r="393" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A393">
-        <f t="shared" si="6"/>
-        <v>393</v>
-      </c>
-      <c r="B393" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A393,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>15818.868104319936</v>
-      </c>
-    </row>
-    <row r="394" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A394">
-        <f t="shared" si="6"/>
-        <v>394</v>
-      </c>
-      <c r="B394" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A394,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>15859.84170805943</v>
-      </c>
-    </row>
-    <row r="395" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A395">
-        <f t="shared" si="6"/>
-        <v>395</v>
-      </c>
-      <c r="B395" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A395,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>15900.815311798924</v>
-      </c>
-    </row>
-    <row r="396" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A396">
-        <f t="shared" si="6"/>
-        <v>396</v>
-      </c>
-      <c r="B396" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A396,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>15941.788915538418</v>
-      </c>
-    </row>
-    <row r="397" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A397">
-        <f t="shared" si="6"/>
-        <v>397</v>
-      </c>
-      <c r="B397" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A397,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>15982.762519277912</v>
-      </c>
-    </row>
-    <row r="398" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A398">
-        <f t="shared" si="6"/>
-        <v>398</v>
-      </c>
-      <c r="B398" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A398,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>16023.736123017406</v>
-      </c>
-    </row>
-    <row r="399" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A399">
-        <f t="shared" si="6"/>
-        <v>399</v>
-      </c>
-      <c r="B399" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A399,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>16064.709726756901</v>
-      </c>
-    </row>
-    <row r="400" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A400">
-        <f t="shared" si="6"/>
-        <v>400</v>
-      </c>
-      <c r="B400" s="1">
-        <f>_xlfn.FORECAST.LINEAR(A400,house!$B$2:$B$546,house!$A$2:$A$546)</f>
-        <v>16105.683330496393</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/house/house.xlsx
+++ b/data/house/house.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\conta\git-CVC\Formation\Python\Industrie\git_indus\data\house\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE9D68EA-A56E-4967-8170-226BB2633C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE2190D-965D-4117-9A74-80065AC21195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="house" sheetId="1" r:id="rId1"/>
@@ -3970,6 +3970,1179 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1048576"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>63</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>73</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>81</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>101</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>106</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>109</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>111</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>112</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>113</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>114</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>116</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>117</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>118</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>119</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>121</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>122</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>123</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>124</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>125</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>126</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>127</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>128</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>129</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>131</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>132</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>133</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>134</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>136</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>137</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>138</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>139</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>141</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>142</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>143</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>144</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>146</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>147</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>148</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>149</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>151</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>152</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>153</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>154</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>156</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>157</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>158</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>159</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>161</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>163</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>164</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>166</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>167</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>168</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>169</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>171</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>172</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>173</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>174</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>176</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>177</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>178</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>179</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>181</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>182</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>183</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>184</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>185</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>186</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>187</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>188</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>189</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>190</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>191</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>193</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>194</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>195</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>196</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>197</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>198</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>199</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>201</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>202</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>203</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>204</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>205</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>206</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>207</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>208</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>209</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>210</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>211</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>212</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>213</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>214</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>215</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>216</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>217</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>218</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>219</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>220</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>221</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>222</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>223</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>224</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>225</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>226</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>227</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>228</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>229</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>230</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>231</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>232</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>233</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>234</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>235</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>236</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>237</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>238</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>239</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>240</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>241</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>242</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>243</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>244</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>245</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>246</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>247</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>248</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>249</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>251</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>252</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>253</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>254</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>255</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>256</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>257</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>258</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>259</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>260</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>261</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>262</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>263</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>264</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>265</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>266</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>267</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>268</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>269</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>270</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>271</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>272</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>273</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>274</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>275</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>276</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>277</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>278</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>279</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>280</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>281</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>282</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>283</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>284</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>285</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>286</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>287</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>288</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>289</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>290</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>291</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>292</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>293</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>294</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>295</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>296</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>297</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>298</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>299</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>301</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>302</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>303</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>304</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>305</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>306</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>307</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>308</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>309</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>310</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>311</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>312</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>313</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>314</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>315</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>316</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>317</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>318</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>319</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>320</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>321</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>322</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>323</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>324</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>325</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>326</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>327</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>328</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>329</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>330</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>331</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>332</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>333</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>334</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>335</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>336</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>337</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>338</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>339</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>340</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>341</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>342</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>343</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>344</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>345</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>346</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>347</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>348</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>349</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>351</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>352</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>353</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>354</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>355</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>356</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>357</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>358</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>359</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>360</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>361</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>362</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>363</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>364</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>365</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>366</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>367</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>368</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>369</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>370</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>371</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>372</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>373</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>374</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>375</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>376</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>377</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>378</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>379</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>380</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>381</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>382</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>383</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>384</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>385</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>386</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>387</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>388</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>389</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>390</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>391</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>392</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>393</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>394</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>395</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>396</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>397</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>398</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>399</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>400</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -3979,6 +5152,1179 @@
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="1048576"/>
+                <c:pt idx="0">
+                  <c:v>125.97787209377151</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>166.95147583326542</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>207.92507957275927</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>248.89868331225318</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>289.87228705174709</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>330.845890791241</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>371.81949453073491</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>412.79309827022882</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>453.76670200972274</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>494.74030574921665</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>535.71390948871056</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>576.68751322820447</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>617.66111696769838</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>658.63472070719229</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>699.60832444668608</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>740.58192818617999</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>781.5555319256739</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>822.52913566516781</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>863.50273940466172</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>904.47634314415563</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>945.44994688364955</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>986.42355062314346</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1027.3971543626374</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1068.3707581021313</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1109.3443618416252</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1150.3179655811191</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1191.291569320613</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1232.2651730601069</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1273.2387767996008</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1314.2123805390947</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1355.1859842785886</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1396.1595880180826</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1437.1331917575765</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1478.1067954970704</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1519.0803992365643</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1560.0540029760582</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1601.0276067155521</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1642.001210455046</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1682.9748141945397</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1723.9484179340336</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1764.9220216735275</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1805.8956254130217</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1846.8692291525153</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1887.8428328920095</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1928.8164366315032</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1969.7900403709973</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>2010.763644110491</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2051.7372478499851</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>2092.7108515894788</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>2133.6844553289729</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>2174.6580590684666</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>2215.6316628079608</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>2256.6052665474544</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>2297.5788702869486</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>2338.5524740264423</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>2379.526077765936</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>2420.4996815054301</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>2461.4732852449238</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>2502.4468889844179</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>2543.4204927239116</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>2584.3940964634057</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>2625.3677002028994</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>2666.3413039423936</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>2707.3149076818872</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>2748.2885114213814</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>2789.2621151608751</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>2830.2357189003692</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>2871.2093226398629</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>2912.182926379357</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>2953.1565301188507</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>2994.1301338583448</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>3035.1037375978385</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>3076.0773413373327</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>3117.0509450768263</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>3158.0245488163205</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>3198.9981525558142</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>3239.9717562953083</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>3280.945360034802</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>3321.9189637742961</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>3362.8925675137898</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>3403.8661712532839</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>3444.8397749927776</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>3485.8133787322718</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>3526.7869824717654</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>3567.7605862112596</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>3608.7341899507533</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>3649.7077936902469</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>3690.6813974297411</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>3731.6550011692348</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>3772.6286049087289</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>3813.6022086482226</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>3854.5758123877167</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>3895.5494161272109</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>3936.5230198667041</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>3977.4966236061982</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>4018.4702273456924</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>4059.4438310851865</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>4100.4174348246797</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>4141.3910385641739</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>4182.364642303668</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>4223.3382460431621</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>4264.3118497826554</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>4305.2854535221495</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>4346.2590572616436</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>4387.2326610011378</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>4428.206264740631</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>4469.1798684801252</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>4510.1534722196193</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>4551.1270759591134</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>4592.1006796986067</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>4633.0742834381008</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>4674.0478871775949</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>4715.0214909170891</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>4755.9950946565823</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>4796.9686983960764</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>4837.9423021355706</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>4878.9159058750647</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>4919.8895096145579</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>4960.8631133540521</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>5001.8367170935462</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>5042.8103208330394</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>5083.7839245725336</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>5124.7575283120277</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>5165.7311320515219</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>5206.7047357910151</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>5247.6783395305092</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>5288.6519432700034</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>5329.6255470094975</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>5370.5991507489907</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>5411.5727544884849</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>5452.546358227979</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>5493.5199619674731</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>5534.4935657069664</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>5575.4671694464605</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>5616.4407731859546</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>5657.4143769254488</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>5698.387980664942</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>5739.3615844044361</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>5780.3351881439303</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>5821.3087918834244</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>5862.2823956229176</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>5903.2559993624118</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>5944.2296031019059</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>5985.2032068414001</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>6026.1768105808933</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>6067.1504143203874</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>6108.1240180598816</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>6149.0976217993757</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>6190.0712255388689</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>6231.0448292783631</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>6272.0184330178572</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>6312.9920367573504</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>6353.9656404968446</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>6394.9392442363387</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>6435.9128479758328</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>6476.8864517153261</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>6517.8600554548202</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>6558.8336591943144</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>6599.8072629338085</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>6640.7808666733017</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>6681.7544704127959</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>6722.72807415229</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>6763.7016778917841</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>6804.6752816312774</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>6845.6488853707715</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>6886.6224891102656</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>6927.5960928497598</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>6968.569696589253</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>7009.5433003287471</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>7050.5169040682413</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>7091.4905078077354</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>7132.4641115472286</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>7173.4377152867228</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>7214.4113190262169</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>7255.3849227657111</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>7296.3585265052043</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>7337.3321302446984</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>7378.3057339841926</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>7419.2793377236867</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>7460.2529414631799</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>7501.2265452026741</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>7542.2001489421682</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>7583.1737526816614</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>7624.1473564211556</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>7665.1209601606497</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>7706.0945639001438</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>7747.0681676396371</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>7788.0417713791312</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>7829.0153751186253</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>7869.9889788581195</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>7910.9625825976127</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>7951.9361863371068</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>7992.909790076601</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>8033.8833938160951</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>8074.8569975555893</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>8115.8306012950834</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>8156.8042050345757</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>8197.7778087740699</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>8238.751412513564</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>8279.7250162530581</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>8320.6986199925523</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>8361.6722237320464</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>8402.6458274715405</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>8443.6194312110347</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>8484.593034950527</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>8525.5666386900211</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>8566.5402424295153</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>8607.5138461690094</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>8648.4874499085035</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>8689.4610536479977</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>8730.4346573874918</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>8771.408261126986</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>8812.3818648664783</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>8853.3554686059724</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>8894.3290723454666</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>8935.3026760849607</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>8976.2762798244548</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>9017.249883563949</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>9058.2234873034431</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>9099.1970910429354</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>9140.1706947824296</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>9181.1442985219237</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>9222.1179022614178</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>9263.091506000912</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>9304.0651097404061</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>9345.0387134799003</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>9386.0123172193944</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>9426.9859209588867</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>9467.9595246983808</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>9508.933128437875</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>9549.9067321773691</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>9590.8803359168633</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>9631.8539396563574</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>9672.8275433958515</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>9713.8011471353457</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>9754.774750874838</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>9795.7483546143321</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>9836.7219583538263</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>9877.6955620933204</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>9918.6691658328145</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>9959.6427695723087</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>10000.616373311803</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>10041.589977051297</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>10082.563580790789</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>10123.537184530283</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>10164.510788269778</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>10205.484392009272</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>10246.457995748766</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>10287.43159948826</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>10328.405203227754</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>10369.378806967246</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>10410.352410706741</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>10451.326014446235</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>10492.299618185729</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>10533.273221925223</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>10574.246825664717</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>10615.220429404211</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>10656.194033143705</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>10697.167636883198</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>10738.141240622692</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>10779.114844362186</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>10820.08844810168</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>10861.062051841174</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>10902.035655580668</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>10943.009259320163</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>10983.982863059657</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>11024.956466799149</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>11065.930070538643</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>11106.903674278137</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>11147.877278017631</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>11188.850881757126</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>11229.82448549662</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>11270.798089236114</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>11311.771692975608</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>11352.7452967151</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>11393.718900454594</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>11434.692504194089</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>11475.666107933583</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>11516.639711673077</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>11557.613315412571</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>11598.586919152065</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>11639.560522891557</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>11680.534126631052</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>11721.507730370546</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>11762.48133411004</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>11803.454937849534</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>11844.428541589028</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>11885.402145328522</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>11926.375749068016</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>11967.349352807509</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>12008.322956547003</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>12049.296560286497</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>12090.270164025991</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>12131.243767765485</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>12172.217371504979</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>12213.190975244474</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>12254.164578983968</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>12295.13818272346</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>12336.111786462954</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>12377.085390202448</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>12418.058993941942</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>12459.032597681437</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>12500.006201420931</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>12540.979805160425</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>12581.953408899919</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>12622.927012639411</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>12663.900616378905</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>12704.8742201184</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>12745.847823857894</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>12786.821427597388</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>12827.795031336882</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>12868.768635076376</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>12909.742238815868</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>12950.715842555363</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>12991.689446294857</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>13032.663050034351</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>13073.636653773845</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>13114.610257513339</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>13155.583861252833</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>13196.557464992327</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>13237.53106873182</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>13278.504672471314</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>13319.478276210808</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>13360.451879950302</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>13401.425483689796</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>13442.39908742929</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>13483.372691168785</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>13524.346294908279</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>13565.319898647771</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>13606.293502387265</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>13647.267106126759</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>13688.240709866253</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>13729.214313605748</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>13770.187917345242</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>13811.161521084736</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>13852.13512482423</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>13893.108728563722</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>13934.082332303216</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>13975.055936042711</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>14016.029539782205</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>14057.003143521699</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>14097.976747261193</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>14138.950351000687</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>14179.923954740179</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>14220.897558479674</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>14261.871162219168</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>14302.844765958662</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>14343.818369698156</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>14384.79197343765</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>14425.765577177144</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>14466.739180916638</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>14507.712784656131</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>14548.686388395625</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>14589.659992135119</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>14630.633595874613</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>14671.607199614107</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>14712.580803353601</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>14753.554407093096</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>14794.52801083259</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>14835.501614572082</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>14876.475218311576</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>14917.44882205107</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>14958.422425790564</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>14999.396029530059</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>15040.369633269553</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>15081.343237009047</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>15122.316840748541</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>15163.290444488033</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>15204.264048227527</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>15245.237651967022</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>15286.211255706516</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>15327.18485944601</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>15368.158463185504</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>15409.132066924998</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>15450.10567066449</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>15491.079274403985</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>15532.052878143479</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>15573.026481882973</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>15614.000085622467</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>15654.973689361961</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>15695.947293101455</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>15736.920896840949</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>15777.894500580442</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>15818.868104319936</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>15859.84170805943</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>15900.815311798924</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>15941.788915538418</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>15982.762519277912</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>16023.736123017406</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>16064.709726756901</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>16105.683330496393</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -9414,12 +11760,3922 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BFFF5B0-594D-4D72-8DA1-9DC10F207B07}">
-  <dimension ref="B1"/>
+  <dimension ref="A1:B391"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.5546875" style="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A1,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>125.97787209377151</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <f>A1+1</f>
+        <v>11</v>
+      </c>
+      <c r="B2" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A2,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>166.95147583326542</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <f t="shared" ref="A3:A66" si="0">A2+1</f>
+        <v>12</v>
+      </c>
+      <c r="B3" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A3,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>207.92507957275927</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B4" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A4,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>248.89868331225318</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B5" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A5,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>289.87228705174709</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B6" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A6,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>330.845890791241</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B7" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A7,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>371.81949453073491</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B8" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A8,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>412.79309827022882</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B9" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A9,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>453.76670200972274</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B10" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A10,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>494.74030574921665</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B11" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A11,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>535.71390948871056</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B12" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A12,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>576.68751322820447</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B13" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A13,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>617.66111696769838</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B14" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A14,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>658.63472070719229</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B15" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A15,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>699.60832444668608</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B16" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A16,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>740.58192818617999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B17" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A17,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>781.5555319256739</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B18" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A18,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>822.52913566516781</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B19" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A19,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>863.50273940466172</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B20" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A20,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>904.47634314415563</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B21" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A21,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>945.44994688364955</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B22" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A22,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>986.42355062314346</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B23" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A23,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>1027.3971543626374</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B24" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A24,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>1068.3707581021313</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="B25" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A25,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>1109.3443618416252</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B26" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A26,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>1150.3179655811191</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B27" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A27,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>1191.291569320613</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B28" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A28,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>1232.2651730601069</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B29" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A29,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>1273.2387767996008</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B30" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A30,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>1314.2123805390947</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="B31" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A31,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>1355.1859842785886</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="B32" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A32,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>1396.1595880180826</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="B33" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A33,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>1437.1331917575765</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="B34" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A34,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>1478.1067954970704</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="B35" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A35,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>1519.0803992365643</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="B36" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A36,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>1560.0540029760582</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="B37" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A37,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>1601.0276067155521</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="B38" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A38,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>1642.001210455046</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="B39" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A39,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>1682.9748141945397</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="B40" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A40,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>1723.9484179340336</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="B41" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A41,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>1764.9220216735275</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="B42" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A42,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>1805.8956254130217</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="B43" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A43,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>1846.8692291525153</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="B44" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A44,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>1887.8428328920095</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="B45" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A45,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>1928.8164366315032</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="B46" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A46,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>1969.7900403709973</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="B47" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A47,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>2010.763644110491</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+      <c r="B48" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A48,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>2051.7372478499851</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="B49" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A49,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>2092.7108515894788</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="B50" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A50,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>2133.6844553289729</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="B51" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A51,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>2174.6580590684666</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="B52" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A52,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>2215.6316628079608</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="B53" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A53,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>2256.6052665474544</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="B54" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A54,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>2297.5788702869486</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="B55" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A55,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>2338.5524740264423</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="B56" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A56,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>2379.526077765936</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
+      <c r="B57" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A57,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>2420.4996815054301</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <f t="shared" si="0"/>
+        <v>67</v>
+      </c>
+      <c r="B58" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A58,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>2461.4732852449238</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <f t="shared" si="0"/>
+        <v>68</v>
+      </c>
+      <c r="B59" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A59,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>2502.4468889844179</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <f t="shared" si="0"/>
+        <v>69</v>
+      </c>
+      <c r="B60" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A60,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>2543.4204927239116</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="B61" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A61,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>2584.3940964634057</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <f t="shared" si="0"/>
+        <v>71</v>
+      </c>
+      <c r="B62" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A62,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>2625.3677002028994</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="B63" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A63,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>2666.3413039423936</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <f t="shared" si="0"/>
+        <v>73</v>
+      </c>
+      <c r="B64" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A64,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>2707.3149076818872</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <f t="shared" si="0"/>
+        <v>74</v>
+      </c>
+      <c r="B65" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A65,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>2748.2885114213814</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
+      <c r="B66" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A66,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>2789.2621151608751</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <f t="shared" ref="A67:A130" si="1">A66+1</f>
+        <v>76</v>
+      </c>
+      <c r="B67" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A67,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>2830.2357189003692</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <f t="shared" si="1"/>
+        <v>77</v>
+      </c>
+      <c r="B68" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A68,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>2871.2093226398629</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <f t="shared" si="1"/>
+        <v>78</v>
+      </c>
+      <c r="B69" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A69,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>2912.182926379357</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <f t="shared" si="1"/>
+        <v>79</v>
+      </c>
+      <c r="B70" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A70,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>2953.1565301188507</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="B71" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A71,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>2994.1301338583448</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <f t="shared" si="1"/>
+        <v>81</v>
+      </c>
+      <c r="B72" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A72,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>3035.1037375978385</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <f t="shared" si="1"/>
+        <v>82</v>
+      </c>
+      <c r="B73" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A73,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>3076.0773413373327</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <f t="shared" si="1"/>
+        <v>83</v>
+      </c>
+      <c r="B74" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A74,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>3117.0509450768263</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <f t="shared" si="1"/>
+        <v>84</v>
+      </c>
+      <c r="B75" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A75,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>3158.0245488163205</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <f t="shared" si="1"/>
+        <v>85</v>
+      </c>
+      <c r="B76" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A76,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>3198.9981525558142</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <f t="shared" si="1"/>
+        <v>86</v>
+      </c>
+      <c r="B77" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A77,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>3239.9717562953083</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <f t="shared" si="1"/>
+        <v>87</v>
+      </c>
+      <c r="B78" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A78,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>3280.945360034802</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+      <c r="B79" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A79,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>3321.9189637742961</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <f t="shared" si="1"/>
+        <v>89</v>
+      </c>
+      <c r="B80" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A80,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>3362.8925675137898</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+      <c r="B81" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A81,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>3403.8661712532839</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <f t="shared" si="1"/>
+        <v>91</v>
+      </c>
+      <c r="B82" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A82,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>3444.8397749927776</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <f t="shared" si="1"/>
+        <v>92</v>
+      </c>
+      <c r="B83" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A83,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>3485.8133787322718</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <f t="shared" si="1"/>
+        <v>93</v>
+      </c>
+      <c r="B84" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A84,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>3526.7869824717654</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <f t="shared" si="1"/>
+        <v>94</v>
+      </c>
+      <c r="B85" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A85,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>3567.7605862112596</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+      <c r="B86" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A86,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>3608.7341899507533</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <f t="shared" si="1"/>
+        <v>96</v>
+      </c>
+      <c r="B87" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A87,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>3649.7077936902469</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <f t="shared" si="1"/>
+        <v>97</v>
+      </c>
+      <c r="B88" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A88,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>3690.6813974297411</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <f t="shared" si="1"/>
+        <v>98</v>
+      </c>
+      <c r="B89" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A89,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>3731.6550011692348</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <f t="shared" si="1"/>
+        <v>99</v>
+      </c>
+      <c r="B90" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A90,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>3772.6286049087289</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="B91" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A91,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>3813.6022086482226</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <f t="shared" si="1"/>
+        <v>101</v>
+      </c>
+      <c r="B92" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A92,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>3854.5758123877167</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <f t="shared" si="1"/>
+        <v>102</v>
+      </c>
+      <c r="B93" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A93,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>3895.5494161272109</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <f t="shared" si="1"/>
+        <v>103</v>
+      </c>
+      <c r="B94" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A94,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>3936.5230198667041</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <f t="shared" si="1"/>
+        <v>104</v>
+      </c>
+      <c r="B95" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A95,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>3977.4966236061982</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+      <c r="B96" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A96,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>4018.4702273456924</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <f t="shared" si="1"/>
+        <v>106</v>
+      </c>
+      <c r="B97" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A97,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>4059.4438310851865</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <f t="shared" si="1"/>
+        <v>107</v>
+      </c>
+      <c r="B98" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A98,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>4100.4174348246797</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <f t="shared" si="1"/>
+        <v>108</v>
+      </c>
+      <c r="B99" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A99,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>4141.3910385641739</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <f t="shared" si="1"/>
+        <v>109</v>
+      </c>
+      <c r="B100" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A100,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>4182.364642303668</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <f t="shared" si="1"/>
+        <v>110</v>
+      </c>
+      <c r="B101" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A101,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>4223.3382460431621</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A102">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="B102" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A102,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>4264.3118497826554</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A103">
+        <f t="shared" si="1"/>
+        <v>112</v>
+      </c>
+      <c r="B103" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A103,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>4305.2854535221495</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A104">
+        <f t="shared" si="1"/>
+        <v>113</v>
+      </c>
+      <c r="B104" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A104,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>4346.2590572616436</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A105">
+        <f t="shared" si="1"/>
+        <v>114</v>
+      </c>
+      <c r="B105" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A105,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>4387.2326610011378</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A106">
+        <f t="shared" si="1"/>
+        <v>115</v>
+      </c>
+      <c r="B106" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A106,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>4428.206264740631</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A107">
+        <f t="shared" si="1"/>
+        <v>116</v>
+      </c>
+      <c r="B107" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A107,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>4469.1798684801252</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A108">
+        <f t="shared" si="1"/>
+        <v>117</v>
+      </c>
+      <c r="B108" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A108,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>4510.1534722196193</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A109">
+        <f t="shared" si="1"/>
+        <v>118</v>
+      </c>
+      <c r="B109" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A109,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>4551.1270759591134</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A110">
+        <f t="shared" si="1"/>
+        <v>119</v>
+      </c>
+      <c r="B110" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A110,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>4592.1006796986067</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A111">
+        <f t="shared" si="1"/>
+        <v>120</v>
+      </c>
+      <c r="B111" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A111,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>4633.0742834381008</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A112">
+        <f t="shared" si="1"/>
+        <v>121</v>
+      </c>
+      <c r="B112" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A112,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>4674.0478871775949</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A113">
+        <f t="shared" si="1"/>
+        <v>122</v>
+      </c>
+      <c r="B113" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A113,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>4715.0214909170891</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A114">
+        <f t="shared" si="1"/>
+        <v>123</v>
+      </c>
+      <c r="B114" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A114,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>4755.9950946565823</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A115">
+        <f t="shared" si="1"/>
+        <v>124</v>
+      </c>
+      <c r="B115" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A115,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>4796.9686983960764</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A116">
+        <f t="shared" si="1"/>
+        <v>125</v>
+      </c>
+      <c r="B116" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A116,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>4837.9423021355706</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A117">
+        <f t="shared" si="1"/>
+        <v>126</v>
+      </c>
+      <c r="B117" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A117,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>4878.9159058750647</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A118">
+        <f t="shared" si="1"/>
+        <v>127</v>
+      </c>
+      <c r="B118" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A118,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>4919.8895096145579</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A119">
+        <f t="shared" si="1"/>
+        <v>128</v>
+      </c>
+      <c r="B119" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A119,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>4960.8631133540521</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A120">
+        <f t="shared" si="1"/>
+        <v>129</v>
+      </c>
+      <c r="B120" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A120,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>5001.8367170935462</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A121">
+        <f t="shared" si="1"/>
+        <v>130</v>
+      </c>
+      <c r="B121" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A121,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>5042.8103208330394</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A122">
+        <f t="shared" si="1"/>
+        <v>131</v>
+      </c>
+      <c r="B122" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A122,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>5083.7839245725336</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A123">
+        <f t="shared" si="1"/>
+        <v>132</v>
+      </c>
+      <c r="B123" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A123,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>5124.7575283120277</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A124">
+        <f t="shared" si="1"/>
+        <v>133</v>
+      </c>
+      <c r="B124" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A124,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>5165.7311320515219</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A125">
+        <f t="shared" si="1"/>
+        <v>134</v>
+      </c>
+      <c r="B125" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A125,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>5206.7047357910151</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A126">
+        <f t="shared" si="1"/>
+        <v>135</v>
+      </c>
+      <c r="B126" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A126,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>5247.6783395305092</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A127">
+        <f t="shared" si="1"/>
+        <v>136</v>
+      </c>
+      <c r="B127" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A127,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>5288.6519432700034</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A128">
+        <f t="shared" si="1"/>
+        <v>137</v>
+      </c>
+      <c r="B128" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A128,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>5329.6255470094975</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A129">
+        <f t="shared" si="1"/>
+        <v>138</v>
+      </c>
+      <c r="B129" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A129,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>5370.5991507489907</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A130">
+        <f t="shared" si="1"/>
+        <v>139</v>
+      </c>
+      <c r="B130" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A130,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>5411.5727544884849</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A131">
+        <f t="shared" ref="A131:A194" si="2">A130+1</f>
+        <v>140</v>
+      </c>
+      <c r="B131" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A131,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>5452.546358227979</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A132">
+        <f t="shared" si="2"/>
+        <v>141</v>
+      </c>
+      <c r="B132" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A132,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>5493.5199619674731</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A133">
+        <f t="shared" si="2"/>
+        <v>142</v>
+      </c>
+      <c r="B133" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A133,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>5534.4935657069664</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A134">
+        <f t="shared" si="2"/>
+        <v>143</v>
+      </c>
+      <c r="B134" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A134,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>5575.4671694464605</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A135">
+        <f t="shared" si="2"/>
+        <v>144</v>
+      </c>
+      <c r="B135" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A135,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>5616.4407731859546</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A136">
+        <f t="shared" si="2"/>
+        <v>145</v>
+      </c>
+      <c r="B136" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A136,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>5657.4143769254488</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A137">
+        <f t="shared" si="2"/>
+        <v>146</v>
+      </c>
+      <c r="B137" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A137,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>5698.387980664942</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A138">
+        <f t="shared" si="2"/>
+        <v>147</v>
+      </c>
+      <c r="B138" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A138,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>5739.3615844044361</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A139">
+        <f t="shared" si="2"/>
+        <v>148</v>
+      </c>
+      <c r="B139" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A139,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>5780.3351881439303</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A140">
+        <f t="shared" si="2"/>
+        <v>149</v>
+      </c>
+      <c r="B140" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A140,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>5821.3087918834244</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A141">
+        <f t="shared" si="2"/>
+        <v>150</v>
+      </c>
+      <c r="B141" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A141,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>5862.2823956229176</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A142">
+        <f t="shared" si="2"/>
+        <v>151</v>
+      </c>
+      <c r="B142" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A142,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>5903.2559993624118</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A143">
+        <f t="shared" si="2"/>
+        <v>152</v>
+      </c>
+      <c r="B143" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A143,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>5944.2296031019059</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A144">
+        <f t="shared" si="2"/>
+        <v>153</v>
+      </c>
+      <c r="B144" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A144,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>5985.2032068414001</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A145">
+        <f t="shared" si="2"/>
+        <v>154</v>
+      </c>
+      <c r="B145" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A145,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>6026.1768105808933</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A146">
+        <f t="shared" si="2"/>
+        <v>155</v>
+      </c>
+      <c r="B146" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A146,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>6067.1504143203874</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A147">
+        <f t="shared" si="2"/>
+        <v>156</v>
+      </c>
+      <c r="B147" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A147,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>6108.1240180598816</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A148">
+        <f t="shared" si="2"/>
+        <v>157</v>
+      </c>
+      <c r="B148" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A148,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>6149.0976217993757</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A149">
+        <f t="shared" si="2"/>
+        <v>158</v>
+      </c>
+      <c r="B149" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A149,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>6190.0712255388689</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A150">
+        <f t="shared" si="2"/>
+        <v>159</v>
+      </c>
+      <c r="B150" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A150,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>6231.0448292783631</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A151">
+        <f t="shared" si="2"/>
+        <v>160</v>
+      </c>
+      <c r="B151" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A151,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>6272.0184330178572</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A152">
+        <f t="shared" si="2"/>
+        <v>161</v>
+      </c>
+      <c r="B152" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A152,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>6312.9920367573504</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A153">
+        <f t="shared" si="2"/>
+        <v>162</v>
+      </c>
+      <c r="B153" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A153,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>6353.9656404968446</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A154">
+        <f t="shared" si="2"/>
+        <v>163</v>
+      </c>
+      <c r="B154" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A154,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>6394.9392442363387</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A155">
+        <f t="shared" si="2"/>
+        <v>164</v>
+      </c>
+      <c r="B155" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A155,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>6435.9128479758328</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A156">
+        <f t="shared" si="2"/>
+        <v>165</v>
+      </c>
+      <c r="B156" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A156,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>6476.8864517153261</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A157">
+        <f t="shared" si="2"/>
+        <v>166</v>
+      </c>
+      <c r="B157" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A157,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>6517.8600554548202</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A158">
+        <f t="shared" si="2"/>
+        <v>167</v>
+      </c>
+      <c r="B158" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A158,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>6558.8336591943144</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A159">
+        <f t="shared" si="2"/>
+        <v>168</v>
+      </c>
+      <c r="B159" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A159,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>6599.8072629338085</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A160">
+        <f t="shared" si="2"/>
+        <v>169</v>
+      </c>
+      <c r="B160" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A160,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>6640.7808666733017</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A161">
+        <f t="shared" si="2"/>
+        <v>170</v>
+      </c>
+      <c r="B161" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A161,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>6681.7544704127959</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A162">
+        <f t="shared" si="2"/>
+        <v>171</v>
+      </c>
+      <c r="B162" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A162,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>6722.72807415229</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A163">
+        <f t="shared" si="2"/>
+        <v>172</v>
+      </c>
+      <c r="B163" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A163,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>6763.7016778917841</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A164">
+        <f t="shared" si="2"/>
+        <v>173</v>
+      </c>
+      <c r="B164" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A164,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>6804.6752816312774</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A165">
+        <f t="shared" si="2"/>
+        <v>174</v>
+      </c>
+      <c r="B165" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A165,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>6845.6488853707715</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A166">
+        <f t="shared" si="2"/>
+        <v>175</v>
+      </c>
+      <c r="B166" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A166,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>6886.6224891102656</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A167">
+        <f t="shared" si="2"/>
+        <v>176</v>
+      </c>
+      <c r="B167" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A167,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>6927.5960928497598</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A168">
+        <f t="shared" si="2"/>
+        <v>177</v>
+      </c>
+      <c r="B168" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A168,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>6968.569696589253</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A169">
+        <f t="shared" si="2"/>
+        <v>178</v>
+      </c>
+      <c r="B169" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A169,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>7009.5433003287471</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A170">
+        <f t="shared" si="2"/>
+        <v>179</v>
+      </c>
+      <c r="B170" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A170,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>7050.5169040682413</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A171">
+        <f t="shared" si="2"/>
+        <v>180</v>
+      </c>
+      <c r="B171" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A171,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>7091.4905078077354</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A172">
+        <f t="shared" si="2"/>
+        <v>181</v>
+      </c>
+      <c r="B172" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A172,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>7132.4641115472286</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A173">
+        <f t="shared" si="2"/>
+        <v>182</v>
+      </c>
+      <c r="B173" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A173,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>7173.4377152867228</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A174">
+        <f t="shared" si="2"/>
+        <v>183</v>
+      </c>
+      <c r="B174" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A174,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>7214.4113190262169</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A175">
+        <f t="shared" si="2"/>
+        <v>184</v>
+      </c>
+      <c r="B175" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A175,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>7255.3849227657111</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A176">
+        <f t="shared" si="2"/>
+        <v>185</v>
+      </c>
+      <c r="B176" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A176,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>7296.3585265052043</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A177">
+        <f t="shared" si="2"/>
+        <v>186</v>
+      </c>
+      <c r="B177" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A177,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>7337.3321302446984</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A178">
+        <f t="shared" si="2"/>
+        <v>187</v>
+      </c>
+      <c r="B178" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A178,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>7378.3057339841926</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A179">
+        <f t="shared" si="2"/>
+        <v>188</v>
+      </c>
+      <c r="B179" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A179,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>7419.2793377236867</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A180">
+        <f t="shared" si="2"/>
+        <v>189</v>
+      </c>
+      <c r="B180" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A180,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>7460.2529414631799</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A181">
+        <f t="shared" si="2"/>
+        <v>190</v>
+      </c>
+      <c r="B181" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A181,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>7501.2265452026741</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A182">
+        <f t="shared" si="2"/>
+        <v>191</v>
+      </c>
+      <c r="B182" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A182,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>7542.2001489421682</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A183">
+        <f t="shared" si="2"/>
+        <v>192</v>
+      </c>
+      <c r="B183" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A183,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>7583.1737526816614</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A184">
+        <f t="shared" si="2"/>
+        <v>193</v>
+      </c>
+      <c r="B184" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A184,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>7624.1473564211556</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A185">
+        <f t="shared" si="2"/>
+        <v>194</v>
+      </c>
+      <c r="B185" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A185,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>7665.1209601606497</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A186">
+        <f t="shared" si="2"/>
+        <v>195</v>
+      </c>
+      <c r="B186" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A186,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>7706.0945639001438</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A187">
+        <f t="shared" si="2"/>
+        <v>196</v>
+      </c>
+      <c r="B187" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A187,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>7747.0681676396371</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A188">
+        <f t="shared" si="2"/>
+        <v>197</v>
+      </c>
+      <c r="B188" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A188,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>7788.0417713791312</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A189">
+        <f t="shared" si="2"/>
+        <v>198</v>
+      </c>
+      <c r="B189" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A189,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>7829.0153751186253</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A190">
+        <f t="shared" si="2"/>
+        <v>199</v>
+      </c>
+      <c r="B190" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A190,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>7869.9889788581195</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A191">
+        <f t="shared" si="2"/>
+        <v>200</v>
+      </c>
+      <c r="B191" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A191,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>7910.9625825976127</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A192">
+        <f t="shared" si="2"/>
+        <v>201</v>
+      </c>
+      <c r="B192" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A192,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>7951.9361863371068</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A193">
+        <f t="shared" si="2"/>
+        <v>202</v>
+      </c>
+      <c r="B193" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A193,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>7992.909790076601</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A194">
+        <f t="shared" si="2"/>
+        <v>203</v>
+      </c>
+      <c r="B194" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A194,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>8033.8833938160951</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A195">
+        <f t="shared" ref="A195:A258" si="3">A194+1</f>
+        <v>204</v>
+      </c>
+      <c r="B195" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A195,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>8074.8569975555893</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A196">
+        <f t="shared" si="3"/>
+        <v>205</v>
+      </c>
+      <c r="B196" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A196,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>8115.8306012950834</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A197">
+        <f t="shared" si="3"/>
+        <v>206</v>
+      </c>
+      <c r="B197" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A197,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>8156.8042050345757</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A198">
+        <f t="shared" si="3"/>
+        <v>207</v>
+      </c>
+      <c r="B198" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A198,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>8197.7778087740699</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A199">
+        <f t="shared" si="3"/>
+        <v>208</v>
+      </c>
+      <c r="B199" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A199,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>8238.751412513564</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A200">
+        <f t="shared" si="3"/>
+        <v>209</v>
+      </c>
+      <c r="B200" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A200,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>8279.7250162530581</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A201">
+        <f t="shared" si="3"/>
+        <v>210</v>
+      </c>
+      <c r="B201" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A201,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>8320.6986199925523</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A202">
+        <f t="shared" si="3"/>
+        <v>211</v>
+      </c>
+      <c r="B202" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A202,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>8361.6722237320464</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A203">
+        <f t="shared" si="3"/>
+        <v>212</v>
+      </c>
+      <c r="B203" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A203,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>8402.6458274715405</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A204">
+        <f t="shared" si="3"/>
+        <v>213</v>
+      </c>
+      <c r="B204" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A204,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>8443.6194312110347</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A205">
+        <f t="shared" si="3"/>
+        <v>214</v>
+      </c>
+      <c r="B205" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A205,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>8484.593034950527</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A206">
+        <f t="shared" si="3"/>
+        <v>215</v>
+      </c>
+      <c r="B206" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A206,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>8525.5666386900211</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A207">
+        <f t="shared" si="3"/>
+        <v>216</v>
+      </c>
+      <c r="B207" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A207,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>8566.5402424295153</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A208">
+        <f t="shared" si="3"/>
+        <v>217</v>
+      </c>
+      <c r="B208" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A208,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>8607.5138461690094</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A209">
+        <f t="shared" si="3"/>
+        <v>218</v>
+      </c>
+      <c r="B209" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A209,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>8648.4874499085035</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A210">
+        <f t="shared" si="3"/>
+        <v>219</v>
+      </c>
+      <c r="B210" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A210,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>8689.4610536479977</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A211">
+        <f t="shared" si="3"/>
+        <v>220</v>
+      </c>
+      <c r="B211" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A211,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>8730.4346573874918</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A212">
+        <f t="shared" si="3"/>
+        <v>221</v>
+      </c>
+      <c r="B212" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A212,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>8771.408261126986</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A213">
+        <f t="shared" si="3"/>
+        <v>222</v>
+      </c>
+      <c r="B213" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A213,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>8812.3818648664783</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A214">
+        <f t="shared" si="3"/>
+        <v>223</v>
+      </c>
+      <c r="B214" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A214,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>8853.3554686059724</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A215">
+        <f t="shared" si="3"/>
+        <v>224</v>
+      </c>
+      <c r="B215" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A215,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>8894.3290723454666</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A216">
+        <f t="shared" si="3"/>
+        <v>225</v>
+      </c>
+      <c r="B216" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A216,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>8935.3026760849607</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A217">
+        <f t="shared" si="3"/>
+        <v>226</v>
+      </c>
+      <c r="B217" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A217,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>8976.2762798244548</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A218">
+        <f t="shared" si="3"/>
+        <v>227</v>
+      </c>
+      <c r="B218" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A218,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>9017.249883563949</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A219">
+        <f t="shared" si="3"/>
+        <v>228</v>
+      </c>
+      <c r="B219" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A219,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>9058.2234873034431</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A220">
+        <f t="shared" si="3"/>
+        <v>229</v>
+      </c>
+      <c r="B220" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A220,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>9099.1970910429354</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A221">
+        <f t="shared" si="3"/>
+        <v>230</v>
+      </c>
+      <c r="B221" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A221,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>9140.1706947824296</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A222">
+        <f t="shared" si="3"/>
+        <v>231</v>
+      </c>
+      <c r="B222" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A222,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>9181.1442985219237</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A223">
+        <f t="shared" si="3"/>
+        <v>232</v>
+      </c>
+      <c r="B223" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A223,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>9222.1179022614178</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A224">
+        <f t="shared" si="3"/>
+        <v>233</v>
+      </c>
+      <c r="B224" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A224,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>9263.091506000912</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A225">
+        <f t="shared" si="3"/>
+        <v>234</v>
+      </c>
+      <c r="B225" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A225,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>9304.0651097404061</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A226">
+        <f t="shared" si="3"/>
+        <v>235</v>
+      </c>
+      <c r="B226" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A226,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>9345.0387134799003</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A227">
+        <f t="shared" si="3"/>
+        <v>236</v>
+      </c>
+      <c r="B227" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A227,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>9386.0123172193944</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A228">
+        <f t="shared" si="3"/>
+        <v>237</v>
+      </c>
+      <c r="B228" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A228,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>9426.9859209588867</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A229">
+        <f t="shared" si="3"/>
+        <v>238</v>
+      </c>
+      <c r="B229" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A229,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>9467.9595246983808</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A230">
+        <f t="shared" si="3"/>
+        <v>239</v>
+      </c>
+      <c r="B230" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A230,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>9508.933128437875</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A231">
+        <f t="shared" si="3"/>
+        <v>240</v>
+      </c>
+      <c r="B231" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A231,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>9549.9067321773691</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A232">
+        <f t="shared" si="3"/>
+        <v>241</v>
+      </c>
+      <c r="B232" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A232,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>9590.8803359168633</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A233">
+        <f t="shared" si="3"/>
+        <v>242</v>
+      </c>
+      <c r="B233" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A233,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>9631.8539396563574</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A234">
+        <f t="shared" si="3"/>
+        <v>243</v>
+      </c>
+      <c r="B234" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A234,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>9672.8275433958515</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A235">
+        <f t="shared" si="3"/>
+        <v>244</v>
+      </c>
+      <c r="B235" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A235,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>9713.8011471353457</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A236">
+        <f t="shared" si="3"/>
+        <v>245</v>
+      </c>
+      <c r="B236" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A236,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>9754.774750874838</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A237">
+        <f t="shared" si="3"/>
+        <v>246</v>
+      </c>
+      <c r="B237" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A237,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>9795.7483546143321</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A238">
+        <f t="shared" si="3"/>
+        <v>247</v>
+      </c>
+      <c r="B238" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A238,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>9836.7219583538263</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A239">
+        <f t="shared" si="3"/>
+        <v>248</v>
+      </c>
+      <c r="B239" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A239,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>9877.6955620933204</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A240">
+        <f t="shared" si="3"/>
+        <v>249</v>
+      </c>
+      <c r="B240" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A240,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>9918.6691658328145</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A241">
+        <f t="shared" si="3"/>
+        <v>250</v>
+      </c>
+      <c r="B241" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A241,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>9959.6427695723087</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A242">
+        <f t="shared" si="3"/>
+        <v>251</v>
+      </c>
+      <c r="B242" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A242,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>10000.616373311803</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A243">
+        <f t="shared" si="3"/>
+        <v>252</v>
+      </c>
+      <c r="B243" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A243,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>10041.589977051297</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A244">
+        <f t="shared" si="3"/>
+        <v>253</v>
+      </c>
+      <c r="B244" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A244,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>10082.563580790789</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A245">
+        <f t="shared" si="3"/>
+        <v>254</v>
+      </c>
+      <c r="B245" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A245,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>10123.537184530283</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A246">
+        <f t="shared" si="3"/>
+        <v>255</v>
+      </c>
+      <c r="B246" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A246,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>10164.510788269778</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A247">
+        <f t="shared" si="3"/>
+        <v>256</v>
+      </c>
+      <c r="B247" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A247,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>10205.484392009272</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A248">
+        <f t="shared" si="3"/>
+        <v>257</v>
+      </c>
+      <c r="B248" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A248,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>10246.457995748766</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A249">
+        <f t="shared" si="3"/>
+        <v>258</v>
+      </c>
+      <c r="B249" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A249,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>10287.43159948826</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A250">
+        <f t="shared" si="3"/>
+        <v>259</v>
+      </c>
+      <c r="B250" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A250,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>10328.405203227754</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A251">
+        <f t="shared" si="3"/>
+        <v>260</v>
+      </c>
+      <c r="B251" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A251,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>10369.378806967246</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A252">
+        <f t="shared" si="3"/>
+        <v>261</v>
+      </c>
+      <c r="B252" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A252,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>10410.352410706741</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A253">
+        <f t="shared" si="3"/>
+        <v>262</v>
+      </c>
+      <c r="B253" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A253,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>10451.326014446235</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A254">
+        <f t="shared" si="3"/>
+        <v>263</v>
+      </c>
+      <c r="B254" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A254,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>10492.299618185729</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A255">
+        <f t="shared" si="3"/>
+        <v>264</v>
+      </c>
+      <c r="B255" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A255,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>10533.273221925223</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A256">
+        <f t="shared" si="3"/>
+        <v>265</v>
+      </c>
+      <c r="B256" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A256,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>10574.246825664717</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A257">
+        <f t="shared" si="3"/>
+        <v>266</v>
+      </c>
+      <c r="B257" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A257,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>10615.220429404211</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A258">
+        <f t="shared" si="3"/>
+        <v>267</v>
+      </c>
+      <c r="B258" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A258,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>10656.194033143705</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A259">
+        <f t="shared" ref="A259:A322" si="4">A258+1</f>
+        <v>268</v>
+      </c>
+      <c r="B259" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A259,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>10697.167636883198</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A260">
+        <f t="shared" si="4"/>
+        <v>269</v>
+      </c>
+      <c r="B260" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A260,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>10738.141240622692</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A261">
+        <f t="shared" si="4"/>
+        <v>270</v>
+      </c>
+      <c r="B261" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A261,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>10779.114844362186</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A262">
+        <f t="shared" si="4"/>
+        <v>271</v>
+      </c>
+      <c r="B262" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A262,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>10820.08844810168</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A263">
+        <f t="shared" si="4"/>
+        <v>272</v>
+      </c>
+      <c r="B263" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A263,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>10861.062051841174</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A264">
+        <f t="shared" si="4"/>
+        <v>273</v>
+      </c>
+      <c r="B264" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A264,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>10902.035655580668</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A265">
+        <f t="shared" si="4"/>
+        <v>274</v>
+      </c>
+      <c r="B265" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A265,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>10943.009259320163</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A266">
+        <f t="shared" si="4"/>
+        <v>275</v>
+      </c>
+      <c r="B266" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A266,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>10983.982863059657</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A267">
+        <f t="shared" si="4"/>
+        <v>276</v>
+      </c>
+      <c r="B267" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A267,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>11024.956466799149</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A268">
+        <f t="shared" si="4"/>
+        <v>277</v>
+      </c>
+      <c r="B268" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A268,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>11065.930070538643</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A269">
+        <f t="shared" si="4"/>
+        <v>278</v>
+      </c>
+      <c r="B269" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A269,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>11106.903674278137</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A270">
+        <f t="shared" si="4"/>
+        <v>279</v>
+      </c>
+      <c r="B270" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A270,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>11147.877278017631</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A271">
+        <f t="shared" si="4"/>
+        <v>280</v>
+      </c>
+      <c r="B271" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A271,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>11188.850881757126</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A272">
+        <f t="shared" si="4"/>
+        <v>281</v>
+      </c>
+      <c r="B272" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A272,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>11229.82448549662</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A273">
+        <f t="shared" si="4"/>
+        <v>282</v>
+      </c>
+      <c r="B273" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A273,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>11270.798089236114</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A274">
+        <f t="shared" si="4"/>
+        <v>283</v>
+      </c>
+      <c r="B274" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A274,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>11311.771692975608</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A275">
+        <f t="shared" si="4"/>
+        <v>284</v>
+      </c>
+      <c r="B275" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A275,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>11352.7452967151</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A276">
+        <f t="shared" si="4"/>
+        <v>285</v>
+      </c>
+      <c r="B276" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A276,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>11393.718900454594</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A277">
+        <f t="shared" si="4"/>
+        <v>286</v>
+      </c>
+      <c r="B277" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A277,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>11434.692504194089</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A278">
+        <f t="shared" si="4"/>
+        <v>287</v>
+      </c>
+      <c r="B278" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A278,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>11475.666107933583</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A279">
+        <f t="shared" si="4"/>
+        <v>288</v>
+      </c>
+      <c r="B279" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A279,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>11516.639711673077</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A280">
+        <f t="shared" si="4"/>
+        <v>289</v>
+      </c>
+      <c r="B280" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A280,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>11557.613315412571</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A281">
+        <f t="shared" si="4"/>
+        <v>290</v>
+      </c>
+      <c r="B281" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A281,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>11598.586919152065</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A282">
+        <f t="shared" si="4"/>
+        <v>291</v>
+      </c>
+      <c r="B282" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A282,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>11639.560522891557</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A283">
+        <f t="shared" si="4"/>
+        <v>292</v>
+      </c>
+      <c r="B283" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A283,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>11680.534126631052</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A284">
+        <f t="shared" si="4"/>
+        <v>293</v>
+      </c>
+      <c r="B284" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A284,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>11721.507730370546</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A285">
+        <f t="shared" si="4"/>
+        <v>294</v>
+      </c>
+      <c r="B285" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A285,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>11762.48133411004</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A286">
+        <f t="shared" si="4"/>
+        <v>295</v>
+      </c>
+      <c r="B286" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A286,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>11803.454937849534</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A287">
+        <f t="shared" si="4"/>
+        <v>296</v>
+      </c>
+      <c r="B287" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A287,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>11844.428541589028</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A288">
+        <f t="shared" si="4"/>
+        <v>297</v>
+      </c>
+      <c r="B288" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A288,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>11885.402145328522</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A289">
+        <f t="shared" si="4"/>
+        <v>298</v>
+      </c>
+      <c r="B289" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A289,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>11926.375749068016</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A290">
+        <f t="shared" si="4"/>
+        <v>299</v>
+      </c>
+      <c r="B290" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A290,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>11967.349352807509</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A291">
+        <f t="shared" si="4"/>
+        <v>300</v>
+      </c>
+      <c r="B291" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A291,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>12008.322956547003</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A292">
+        <f t="shared" si="4"/>
+        <v>301</v>
+      </c>
+      <c r="B292" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A292,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>12049.296560286497</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A293">
+        <f t="shared" si="4"/>
+        <v>302</v>
+      </c>
+      <c r="B293" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A293,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>12090.270164025991</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A294">
+        <f t="shared" si="4"/>
+        <v>303</v>
+      </c>
+      <c r="B294" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A294,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>12131.243767765485</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A295">
+        <f t="shared" si="4"/>
+        <v>304</v>
+      </c>
+      <c r="B295" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A295,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>12172.217371504979</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A296">
+        <f t="shared" si="4"/>
+        <v>305</v>
+      </c>
+      <c r="B296" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A296,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>12213.190975244474</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A297">
+        <f t="shared" si="4"/>
+        <v>306</v>
+      </c>
+      <c r="B297" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A297,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>12254.164578983968</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A298">
+        <f t="shared" si="4"/>
+        <v>307</v>
+      </c>
+      <c r="B298" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A298,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>12295.13818272346</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A299">
+        <f t="shared" si="4"/>
+        <v>308</v>
+      </c>
+      <c r="B299" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A299,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>12336.111786462954</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A300">
+        <f t="shared" si="4"/>
+        <v>309</v>
+      </c>
+      <c r="B300" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A300,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>12377.085390202448</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A301">
+        <f t="shared" si="4"/>
+        <v>310</v>
+      </c>
+      <c r="B301" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A301,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>12418.058993941942</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A302">
+        <f t="shared" si="4"/>
+        <v>311</v>
+      </c>
+      <c r="B302" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A302,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>12459.032597681437</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A303">
+        <f t="shared" si="4"/>
+        <v>312</v>
+      </c>
+      <c r="B303" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A303,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>12500.006201420931</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A304">
+        <f t="shared" si="4"/>
+        <v>313</v>
+      </c>
+      <c r="B304" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A304,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>12540.979805160425</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A305">
+        <f t="shared" si="4"/>
+        <v>314</v>
+      </c>
+      <c r="B305" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A305,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>12581.953408899919</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A306">
+        <f t="shared" si="4"/>
+        <v>315</v>
+      </c>
+      <c r="B306" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A306,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>12622.927012639411</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A307">
+        <f t="shared" si="4"/>
+        <v>316</v>
+      </c>
+      <c r="B307" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A307,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>12663.900616378905</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A308">
+        <f t="shared" si="4"/>
+        <v>317</v>
+      </c>
+      <c r="B308" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A308,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>12704.8742201184</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A309">
+        <f t="shared" si="4"/>
+        <v>318</v>
+      </c>
+      <c r="B309" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A309,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>12745.847823857894</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A310">
+        <f t="shared" si="4"/>
+        <v>319</v>
+      </c>
+      <c r="B310" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A310,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>12786.821427597388</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A311">
+        <f t="shared" si="4"/>
+        <v>320</v>
+      </c>
+      <c r="B311" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A311,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>12827.795031336882</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A312">
+        <f t="shared" si="4"/>
+        <v>321</v>
+      </c>
+      <c r="B312" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A312,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>12868.768635076376</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A313">
+        <f t="shared" si="4"/>
+        <v>322</v>
+      </c>
+      <c r="B313" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A313,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>12909.742238815868</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A314">
+        <f t="shared" si="4"/>
+        <v>323</v>
+      </c>
+      <c r="B314" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A314,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>12950.715842555363</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A315">
+        <f t="shared" si="4"/>
+        <v>324</v>
+      </c>
+      <c r="B315" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A315,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>12991.689446294857</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A316">
+        <f t="shared" si="4"/>
+        <v>325</v>
+      </c>
+      <c r="B316" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A316,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>13032.663050034351</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A317">
+        <f t="shared" si="4"/>
+        <v>326</v>
+      </c>
+      <c r="B317" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A317,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>13073.636653773845</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A318">
+        <f t="shared" si="4"/>
+        <v>327</v>
+      </c>
+      <c r="B318" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A318,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>13114.610257513339</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A319">
+        <f t="shared" si="4"/>
+        <v>328</v>
+      </c>
+      <c r="B319" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A319,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>13155.583861252833</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A320">
+        <f t="shared" si="4"/>
+        <v>329</v>
+      </c>
+      <c r="B320" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A320,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>13196.557464992327</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A321">
+        <f t="shared" si="4"/>
+        <v>330</v>
+      </c>
+      <c r="B321" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A321,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>13237.53106873182</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A322">
+        <f t="shared" si="4"/>
+        <v>331</v>
+      </c>
+      <c r="B322" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A322,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>13278.504672471314</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A323">
+        <f t="shared" ref="A323:A386" si="5">A322+1</f>
+        <v>332</v>
+      </c>
+      <c r="B323" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A323,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>13319.478276210808</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A324">
+        <f t="shared" si="5"/>
+        <v>333</v>
+      </c>
+      <c r="B324" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A324,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>13360.451879950302</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A325">
+        <f t="shared" si="5"/>
+        <v>334</v>
+      </c>
+      <c r="B325" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A325,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>13401.425483689796</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A326">
+        <f t="shared" si="5"/>
+        <v>335</v>
+      </c>
+      <c r="B326" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A326,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>13442.39908742929</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A327">
+        <f t="shared" si="5"/>
+        <v>336</v>
+      </c>
+      <c r="B327" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A327,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>13483.372691168785</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A328">
+        <f t="shared" si="5"/>
+        <v>337</v>
+      </c>
+      <c r="B328" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A328,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>13524.346294908279</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A329">
+        <f t="shared" si="5"/>
+        <v>338</v>
+      </c>
+      <c r="B329" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A329,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>13565.319898647771</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A330">
+        <f t="shared" si="5"/>
+        <v>339</v>
+      </c>
+      <c r="B330" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A330,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>13606.293502387265</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A331">
+        <f t="shared" si="5"/>
+        <v>340</v>
+      </c>
+      <c r="B331" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A331,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>13647.267106126759</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A332">
+        <f t="shared" si="5"/>
+        <v>341</v>
+      </c>
+      <c r="B332" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A332,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>13688.240709866253</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A333">
+        <f t="shared" si="5"/>
+        <v>342</v>
+      </c>
+      <c r="B333" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A333,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>13729.214313605748</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A334">
+        <f t="shared" si="5"/>
+        <v>343</v>
+      </c>
+      <c r="B334" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A334,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>13770.187917345242</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A335">
+        <f t="shared" si="5"/>
+        <v>344</v>
+      </c>
+      <c r="B335" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A335,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>13811.161521084736</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A336">
+        <f t="shared" si="5"/>
+        <v>345</v>
+      </c>
+      <c r="B336" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A336,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>13852.13512482423</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A337">
+        <f t="shared" si="5"/>
+        <v>346</v>
+      </c>
+      <c r="B337" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A337,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>13893.108728563722</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A338">
+        <f t="shared" si="5"/>
+        <v>347</v>
+      </c>
+      <c r="B338" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A338,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>13934.082332303216</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A339">
+        <f t="shared" si="5"/>
+        <v>348</v>
+      </c>
+      <c r="B339" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A339,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>13975.055936042711</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A340">
+        <f t="shared" si="5"/>
+        <v>349</v>
+      </c>
+      <c r="B340" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A340,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>14016.029539782205</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A341">
+        <f t="shared" si="5"/>
+        <v>350</v>
+      </c>
+      <c r="B341" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A341,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>14057.003143521699</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A342">
+        <f t="shared" si="5"/>
+        <v>351</v>
+      </c>
+      <c r="B342" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A342,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>14097.976747261193</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A343">
+        <f t="shared" si="5"/>
+        <v>352</v>
+      </c>
+      <c r="B343" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A343,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>14138.950351000687</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A344">
+        <f t="shared" si="5"/>
+        <v>353</v>
+      </c>
+      <c r="B344" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A344,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>14179.923954740179</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A345">
+        <f t="shared" si="5"/>
+        <v>354</v>
+      </c>
+      <c r="B345" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A345,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>14220.897558479674</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A346">
+        <f t="shared" si="5"/>
+        <v>355</v>
+      </c>
+      <c r="B346" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A346,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>14261.871162219168</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A347">
+        <f t="shared" si="5"/>
+        <v>356</v>
+      </c>
+      <c r="B347" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A347,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>14302.844765958662</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A348">
+        <f t="shared" si="5"/>
+        <v>357</v>
+      </c>
+      <c r="B348" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A348,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>14343.818369698156</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A349">
+        <f t="shared" si="5"/>
+        <v>358</v>
+      </c>
+      <c r="B349" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A349,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>14384.79197343765</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A350">
+        <f t="shared" si="5"/>
+        <v>359</v>
+      </c>
+      <c r="B350" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A350,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>14425.765577177144</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A351">
+        <f t="shared" si="5"/>
+        <v>360</v>
+      </c>
+      <c r="B351" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A351,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>14466.739180916638</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A352">
+        <f t="shared" si="5"/>
+        <v>361</v>
+      </c>
+      <c r="B352" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A352,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>14507.712784656131</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A353">
+        <f t="shared" si="5"/>
+        <v>362</v>
+      </c>
+      <c r="B353" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A353,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>14548.686388395625</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A354">
+        <f t="shared" si="5"/>
+        <v>363</v>
+      </c>
+      <c r="B354" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A354,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>14589.659992135119</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A355">
+        <f t="shared" si="5"/>
+        <v>364</v>
+      </c>
+      <c r="B355" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A355,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>14630.633595874613</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A356">
+        <f t="shared" si="5"/>
+        <v>365</v>
+      </c>
+      <c r="B356" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A356,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>14671.607199614107</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A357">
+        <f t="shared" si="5"/>
+        <v>366</v>
+      </c>
+      <c r="B357" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A357,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>14712.580803353601</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A358">
+        <f t="shared" si="5"/>
+        <v>367</v>
+      </c>
+      <c r="B358" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A358,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>14753.554407093096</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A359">
+        <f t="shared" si="5"/>
+        <v>368</v>
+      </c>
+      <c r="B359" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A359,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>14794.52801083259</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A360">
+        <f t="shared" si="5"/>
+        <v>369</v>
+      </c>
+      <c r="B360" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A360,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>14835.501614572082</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A361">
+        <f t="shared" si="5"/>
+        <v>370</v>
+      </c>
+      <c r="B361" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A361,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>14876.475218311576</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A362">
+        <f t="shared" si="5"/>
+        <v>371</v>
+      </c>
+      <c r="B362" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A362,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>14917.44882205107</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A363">
+        <f t="shared" si="5"/>
+        <v>372</v>
+      </c>
+      <c r="B363" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A363,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>14958.422425790564</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A364">
+        <f t="shared" si="5"/>
+        <v>373</v>
+      </c>
+      <c r="B364" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A364,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>14999.396029530059</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A365">
+        <f t="shared" si="5"/>
+        <v>374</v>
+      </c>
+      <c r="B365" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A365,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>15040.369633269553</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A366">
+        <f t="shared" si="5"/>
+        <v>375</v>
+      </c>
+      <c r="B366" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A366,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>15081.343237009047</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A367">
+        <f t="shared" si="5"/>
+        <v>376</v>
+      </c>
+      <c r="B367" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A367,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>15122.316840748541</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A368">
+        <f t="shared" si="5"/>
+        <v>377</v>
+      </c>
+      <c r="B368" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A368,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>15163.290444488033</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A369">
+        <f t="shared" si="5"/>
+        <v>378</v>
+      </c>
+      <c r="B369" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A369,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>15204.264048227527</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A370">
+        <f t="shared" si="5"/>
+        <v>379</v>
+      </c>
+      <c r="B370" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A370,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>15245.237651967022</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A371">
+        <f t="shared" si="5"/>
+        <v>380</v>
+      </c>
+      <c r="B371" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A371,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>15286.211255706516</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A372">
+        <f t="shared" si="5"/>
+        <v>381</v>
+      </c>
+      <c r="B372" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A372,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>15327.18485944601</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A373">
+        <f t="shared" si="5"/>
+        <v>382</v>
+      </c>
+      <c r="B373" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A373,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>15368.158463185504</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A374">
+        <f t="shared" si="5"/>
+        <v>383</v>
+      </c>
+      <c r="B374" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A374,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>15409.132066924998</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A375">
+        <f t="shared" si="5"/>
+        <v>384</v>
+      </c>
+      <c r="B375" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A375,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>15450.10567066449</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A376">
+        <f t="shared" si="5"/>
+        <v>385</v>
+      </c>
+      <c r="B376" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A376,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>15491.079274403985</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A377">
+        <f t="shared" si="5"/>
+        <v>386</v>
+      </c>
+      <c r="B377" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A377,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>15532.052878143479</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A378">
+        <f t="shared" si="5"/>
+        <v>387</v>
+      </c>
+      <c r="B378" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A378,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>15573.026481882973</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A379">
+        <f t="shared" si="5"/>
+        <v>388</v>
+      </c>
+      <c r="B379" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A379,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>15614.000085622467</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A380">
+        <f t="shared" si="5"/>
+        <v>389</v>
+      </c>
+      <c r="B380" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A380,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>15654.973689361961</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A381">
+        <f t="shared" si="5"/>
+        <v>390</v>
+      </c>
+      <c r="B381" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A381,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>15695.947293101455</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A382">
+        <f t="shared" si="5"/>
+        <v>391</v>
+      </c>
+      <c r="B382" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A382,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>15736.920896840949</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A383">
+        <f t="shared" si="5"/>
+        <v>392</v>
+      </c>
+      <c r="B383" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A383,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>15777.894500580442</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A384">
+        <f t="shared" si="5"/>
+        <v>393</v>
+      </c>
+      <c r="B384" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A384,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>15818.868104319936</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A385">
+        <f t="shared" si="5"/>
+        <v>394</v>
+      </c>
+      <c r="B385" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A385,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>15859.84170805943</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A386">
+        <f t="shared" si="5"/>
+        <v>395</v>
+      </c>
+      <c r="B386" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A386,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>15900.815311798924</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A387">
+        <f t="shared" ref="A387:A401" si="6">A386+1</f>
+        <v>396</v>
+      </c>
+      <c r="B387" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A387,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>15941.788915538418</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A388">
+        <f t="shared" si="6"/>
+        <v>397</v>
+      </c>
+      <c r="B388" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A388,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>15982.762519277912</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A389">
+        <f t="shared" si="6"/>
+        <v>398</v>
+      </c>
+      <c r="B389" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A389,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>16023.736123017406</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A390">
+        <f t="shared" si="6"/>
+        <v>399</v>
+      </c>
+      <c r="B390" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A390,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>16064.709726756901</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A391">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="B391" s="1">
+        <f>_xlfn.FORECAST.LINEAR(A391,house!B$2:B$546,house!A$2:A$546)</f>
+        <v>16105.683330496393</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
